--- a/artfynd/A 31945-2021 artfynd.xlsx
+++ b/artfynd/A 31945-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 31945-2021 artfynd.xlsx
+++ b/artfynd/A 31945-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3061,6 +3061,2148 @@
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>121476441</v>
+      </c>
+      <c r="B23" t="n">
+        <v>90709</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Jiltjaurberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>586513</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7275037</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2020-01-15</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2020-01-17</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Isak Sarac</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>121477315</v>
+      </c>
+      <c r="B24" t="n">
+        <v>78604</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Jiltjaurberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>586410</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7274861</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2020-01-15</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2020-01-17</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Isak Sarac</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>121476846</v>
+      </c>
+      <c r="B25" t="n">
+        <v>90705</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Jiltjaurberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>586623</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7275057</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2020-01-15</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2020-01-17</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Isak Sarac</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>121476841</v>
+      </c>
+      <c r="B26" t="n">
+        <v>90705</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Jiltjaurberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>586739</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7274805</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2020-01-15</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2020-01-17</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Isak Sarac</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>121476843</v>
+      </c>
+      <c r="B27" t="n">
+        <v>90705</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Jiltjaurberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>586373</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7275002</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2020-01-15</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2020-01-17</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Isak Sarac</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>121477395</v>
+      </c>
+      <c r="B28" t="n">
+        <v>88031</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>510</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Jiltjaurberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>586434</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7274787</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2020-01-15</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2020-01-17</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Isak Sarac</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>121476790</v>
+      </c>
+      <c r="B29" t="n">
+        <v>78686</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>864</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Jiltjaurberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>586263</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7274991</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2020-01-15</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2020-01-17</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Isak Sarac</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>121477385</v>
+      </c>
+      <c r="B30" t="n">
+        <v>82388</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Jiltjaurberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>586263</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7274991</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2020-01-15</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2020-01-17</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Isak Sarac</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>121476719</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79685</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Jiltjaurberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>586424</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7274747</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2020-01-15</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2020-01-17</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Isak Sarac</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>121476600</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79686</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Jiltjaurberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>586290</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7274978</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2020-01-15</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2020-01-17</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Isak Sarac</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>121477319</v>
+      </c>
+      <c r="B33" t="n">
+        <v>78604</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Jiltjaurberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>586263</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7274991</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2020-01-15</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2020-01-17</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Isak Sarac</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>121476720</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79685</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Jiltjaurberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>586428</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7274782</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2020-01-15</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2020-01-17</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Isak Sarac</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>121476598</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79686</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Jiltjaurberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>586242</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7274946</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2020-01-15</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2020-01-17</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Isak Sarac</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>121476721</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79685</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Jiltjaurberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>586434</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7274787</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2020-01-15</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2020-01-17</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Isak Sarac</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>121476688</v>
+      </c>
+      <c r="B37" t="n">
+        <v>90995</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>658</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Jiltjaurberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>586513</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7275037</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2020-01-15</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2020-01-17</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Isak Sarac</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>121476597</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79686</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Jiltjaurberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>586361</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7274887</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2020-01-15</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2020-01-17</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Isak Sarac</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>121477312</v>
+      </c>
+      <c r="B39" t="n">
+        <v>78604</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Jiltjaurberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>586774</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7274818</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2020-01-15</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2020-01-17</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Isak Sarac</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>121476521</v>
+      </c>
+      <c r="B40" t="n">
+        <v>79551</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>388</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Stiftgelélav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Collema furfuraceum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Arnold) Du Rietz</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Jiltjaurberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>586320</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7274981</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2020-01-15</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2020-01-17</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Isak Sarac</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>121476595</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79686</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Jiltjaurberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>586410</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7274861</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2020-01-15</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2020-01-17</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Isak Sarac</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>121476718</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79685</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Jiltjaurberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>586671</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7274637</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2020-01-15</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2020-01-17</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Isak Sarac</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>121476439</v>
+      </c>
+      <c r="B43" t="n">
+        <v>90709</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Jiltjaurberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>586310</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7274979</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2020-01-15</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2020-01-17</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Isak Sarac</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31945-2021 artfynd.xlsx
+++ b/artfynd/A 31945-2021 artfynd.xlsx
@@ -3063,10 +3063,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121476441</v>
+        <v>121476598</v>
       </c>
       <c r="B23" t="n">
-        <v>90709</v>
+        <v>79686</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3079,21 +3079,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3103,10 +3103,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>586513</v>
+        <v>586242</v>
       </c>
       <c r="R23" t="n">
-        <v>7275037</v>
+        <v>7274946</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3165,10 +3165,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121477315</v>
+        <v>121477385</v>
       </c>
       <c r="B24" t="n">
-        <v>78604</v>
+        <v>82388</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3181,21 +3181,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3205,10 +3205,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>586410</v>
+        <v>586263</v>
       </c>
       <c r="R24" t="n">
-        <v>7274861</v>
+        <v>7274991</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3267,10 +3267,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121476846</v>
+        <v>121476597</v>
       </c>
       <c r="B25" t="n">
-        <v>90705</v>
+        <v>79686</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3283,21 +3283,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3307,10 +3307,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>586623</v>
+        <v>586361</v>
       </c>
       <c r="R25" t="n">
-        <v>7275057</v>
+        <v>7274887</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3369,10 +3369,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121476841</v>
+        <v>121476790</v>
       </c>
       <c r="B26" t="n">
-        <v>90705</v>
+        <v>78686</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3385,21 +3385,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>864</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3409,10 +3409,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>586739</v>
+        <v>586263</v>
       </c>
       <c r="R26" t="n">
-        <v>7274805</v>
+        <v>7274991</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3471,10 +3471,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121476843</v>
+        <v>121477315</v>
       </c>
       <c r="B27" t="n">
-        <v>90705</v>
+        <v>78604</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3487,21 +3487,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>586373</v>
+        <v>586410</v>
       </c>
       <c r="R27" t="n">
-        <v>7275002</v>
+        <v>7274861</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3573,10 +3573,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121477395</v>
+        <v>121476441</v>
       </c>
       <c r="B28" t="n">
-        <v>88031</v>
+        <v>90710</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3589,21 +3589,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>586434</v>
+        <v>586513</v>
       </c>
       <c r="R28" t="n">
-        <v>7274787</v>
+        <v>7275037</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3675,10 +3675,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121476790</v>
+        <v>121476600</v>
       </c>
       <c r="B29" t="n">
-        <v>78686</v>
+        <v>79686</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3691,21 +3691,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3715,10 +3715,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>586263</v>
+        <v>586290</v>
       </c>
       <c r="R29" t="n">
-        <v>7274991</v>
+        <v>7274978</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3777,10 +3777,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121477385</v>
+        <v>121476721</v>
       </c>
       <c r="B30" t="n">
-        <v>82388</v>
+        <v>79685</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3793,21 +3793,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3817,10 +3817,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>586263</v>
+        <v>586434</v>
       </c>
       <c r="R30" t="n">
-        <v>7274991</v>
+        <v>7274787</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3879,10 +3879,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121476719</v>
+        <v>121476843</v>
       </c>
       <c r="B31" t="n">
-        <v>79685</v>
+        <v>90706</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3895,21 +3895,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3919,10 +3919,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>586424</v>
+        <v>586373</v>
       </c>
       <c r="R31" t="n">
-        <v>7274747</v>
+        <v>7275002</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3981,10 +3981,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121476600</v>
+        <v>121476439</v>
       </c>
       <c r="B32" t="n">
-        <v>79686</v>
+        <v>90710</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3997,21 +3997,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4021,10 +4021,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>586290</v>
+        <v>586310</v>
       </c>
       <c r="R32" t="n">
-        <v>7274978</v>
+        <v>7274979</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4083,10 +4083,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121477319</v>
+        <v>121477395</v>
       </c>
       <c r="B33" t="n">
-        <v>78604</v>
+        <v>88031</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4099,21 +4099,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4123,10 +4123,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>586263</v>
+        <v>586434</v>
       </c>
       <c r="R33" t="n">
-        <v>7274991</v>
+        <v>7274787</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4185,10 +4185,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121476720</v>
+        <v>121476846</v>
       </c>
       <c r="B34" t="n">
-        <v>79685</v>
+        <v>90706</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4201,21 +4201,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4225,10 +4225,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>586428</v>
+        <v>586623</v>
       </c>
       <c r="R34" t="n">
-        <v>7274782</v>
+        <v>7275057</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4287,10 +4287,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121476598</v>
+        <v>121476841</v>
       </c>
       <c r="B35" t="n">
-        <v>79686</v>
+        <v>90706</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4303,21 +4303,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4327,10 +4327,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>586242</v>
+        <v>586739</v>
       </c>
       <c r="R35" t="n">
-        <v>7274946</v>
+        <v>7274805</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4389,7 +4389,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121476721</v>
+        <v>121476720</v>
       </c>
       <c r="B36" t="n">
         <v>79685</v>
@@ -4429,10 +4429,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>586434</v>
+        <v>586428</v>
       </c>
       <c r="R36" t="n">
-        <v>7274787</v>
+        <v>7274782</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4491,10 +4491,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121476688</v>
+        <v>121476595</v>
       </c>
       <c r="B37" t="n">
-        <v>90995</v>
+        <v>79686</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4507,21 +4507,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4531,10 +4531,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>586513</v>
+        <v>586410</v>
       </c>
       <c r="R37" t="n">
-        <v>7275037</v>
+        <v>7274861</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4593,10 +4593,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121476597</v>
+        <v>121476719</v>
       </c>
       <c r="B38" t="n">
-        <v>79686</v>
+        <v>79685</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4609,21 +4609,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4633,10 +4633,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>586361</v>
+        <v>586424</v>
       </c>
       <c r="R38" t="n">
-        <v>7274887</v>
+        <v>7274747</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4695,7 +4695,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121477312</v>
+        <v>121477319</v>
       </c>
       <c r="B39" t="n">
         <v>78604</v>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>586774</v>
+        <v>586263</v>
       </c>
       <c r="R39" t="n">
-        <v>7274818</v>
+        <v>7274991</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4797,10 +4797,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121476521</v>
+        <v>121477312</v>
       </c>
       <c r="B40" t="n">
-        <v>79551</v>
+        <v>78604</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4813,21 +4813,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>388</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4837,10 +4837,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>586320</v>
+        <v>586774</v>
       </c>
       <c r="R40" t="n">
-        <v>7274981</v>
+        <v>7274818</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4899,10 +4899,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121476595</v>
+        <v>121476688</v>
       </c>
       <c r="B41" t="n">
-        <v>79686</v>
+        <v>90996</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4915,21 +4915,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4939,10 +4939,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>586410</v>
+        <v>586513</v>
       </c>
       <c r="R41" t="n">
-        <v>7274861</v>
+        <v>7275037</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5001,10 +5001,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121476718</v>
+        <v>121476521</v>
       </c>
       <c r="B42" t="n">
-        <v>79685</v>
+        <v>79551</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5017,21 +5017,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>388</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5041,10 +5041,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>586671</v>
+        <v>586320</v>
       </c>
       <c r="R42" t="n">
-        <v>7274637</v>
+        <v>7274981</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5103,10 +5103,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121476439</v>
+        <v>121476718</v>
       </c>
       <c r="B43" t="n">
-        <v>90709</v>
+        <v>79685</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5119,21 +5119,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5143,10 +5143,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>586310</v>
+        <v>586671</v>
       </c>
       <c r="R43" t="n">
-        <v>7274979</v>
+        <v>7274637</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>

--- a/artfynd/A 31945-2021 artfynd.xlsx
+++ b/artfynd/A 31945-2021 artfynd.xlsx
@@ -3063,10 +3063,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121476598</v>
+        <v>121477395</v>
       </c>
       <c r="B23" t="n">
-        <v>79686</v>
+        <v>88034</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3079,21 +3079,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>510</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3103,10 +3103,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>586242</v>
+        <v>586434</v>
       </c>
       <c r="R23" t="n">
-        <v>7274946</v>
+        <v>7274787</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3165,10 +3165,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121477385</v>
+        <v>121476598</v>
       </c>
       <c r="B24" t="n">
-        <v>82388</v>
+        <v>79689</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3181,21 +3181,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3205,10 +3205,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>586263</v>
+        <v>586242</v>
       </c>
       <c r="R24" t="n">
-        <v>7274991</v>
+        <v>7274946</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3267,10 +3267,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121476597</v>
+        <v>121476441</v>
       </c>
       <c r="B25" t="n">
-        <v>79686</v>
+        <v>90713</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3283,21 +3283,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3307,10 +3307,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>586361</v>
+        <v>586513</v>
       </c>
       <c r="R25" t="n">
-        <v>7274887</v>
+        <v>7275037</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3369,10 +3369,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121476790</v>
+        <v>121476721</v>
       </c>
       <c r="B26" t="n">
-        <v>78686</v>
+        <v>79688</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3385,21 +3385,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>864</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3409,10 +3409,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>586263</v>
+        <v>586434</v>
       </c>
       <c r="R26" t="n">
-        <v>7274991</v>
+        <v>7274787</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3471,10 +3471,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121477315</v>
+        <v>121476846</v>
       </c>
       <c r="B27" t="n">
-        <v>78604</v>
+        <v>90709</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3487,21 +3487,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>586410</v>
+        <v>586623</v>
       </c>
       <c r="R27" t="n">
-        <v>7274861</v>
+        <v>7275057</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3573,10 +3573,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121476441</v>
+        <v>121476688</v>
       </c>
       <c r="B28" t="n">
-        <v>90710</v>
+        <v>90999</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3589,21 +3589,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3675,10 +3675,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121476600</v>
+        <v>121476719</v>
       </c>
       <c r="B29" t="n">
-        <v>79686</v>
+        <v>79688</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3691,21 +3691,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3715,10 +3715,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>586290</v>
+        <v>586424</v>
       </c>
       <c r="R29" t="n">
-        <v>7274978</v>
+        <v>7274747</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3777,10 +3777,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121476721</v>
+        <v>121476841</v>
       </c>
       <c r="B30" t="n">
-        <v>79685</v>
+        <v>90709</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3793,21 +3793,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3817,10 +3817,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>586434</v>
+        <v>586739</v>
       </c>
       <c r="R30" t="n">
-        <v>7274787</v>
+        <v>7274805</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3879,10 +3879,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121476843</v>
+        <v>121476718</v>
       </c>
       <c r="B31" t="n">
-        <v>90706</v>
+        <v>79688</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3895,21 +3895,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3919,10 +3919,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>586373</v>
+        <v>586671</v>
       </c>
       <c r="R31" t="n">
-        <v>7275002</v>
+        <v>7274637</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3984,7 +3984,7 @@
         <v>121476439</v>
       </c>
       <c r="B32" t="n">
-        <v>90710</v>
+        <v>90713</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4083,10 +4083,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121477395</v>
+        <v>121476600</v>
       </c>
       <c r="B33" t="n">
-        <v>88031</v>
+        <v>79689</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4099,21 +4099,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>510</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4123,10 +4123,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>586434</v>
+        <v>586290</v>
       </c>
       <c r="R33" t="n">
-        <v>7274787</v>
+        <v>7274978</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4185,10 +4185,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121476846</v>
+        <v>121477319</v>
       </c>
       <c r="B34" t="n">
-        <v>90706</v>
+        <v>78607</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4201,21 +4201,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4225,10 +4225,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>586623</v>
+        <v>586263</v>
       </c>
       <c r="R34" t="n">
-        <v>7275057</v>
+        <v>7274991</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4287,10 +4287,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121476841</v>
+        <v>121476521</v>
       </c>
       <c r="B35" t="n">
-        <v>90706</v>
+        <v>79554</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4303,21 +4303,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1108</v>
+        <v>388</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4327,10 +4327,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>586739</v>
+        <v>586320</v>
       </c>
       <c r="R35" t="n">
-        <v>7274805</v>
+        <v>7274981</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4389,10 +4389,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121476720</v>
+        <v>121476843</v>
       </c>
       <c r="B36" t="n">
-        <v>79685</v>
+        <v>90709</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4405,21 +4405,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4429,10 +4429,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>586428</v>
+        <v>586373</v>
       </c>
       <c r="R36" t="n">
-        <v>7274782</v>
+        <v>7275002</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4491,10 +4491,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121476595</v>
+        <v>121476720</v>
       </c>
       <c r="B37" t="n">
-        <v>79686</v>
+        <v>79688</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4507,21 +4507,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4531,10 +4531,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>586410</v>
+        <v>586428</v>
       </c>
       <c r="R37" t="n">
-        <v>7274861</v>
+        <v>7274782</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4593,10 +4593,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121476719</v>
+        <v>121476790</v>
       </c>
       <c r="B38" t="n">
-        <v>79685</v>
+        <v>78689</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4609,21 +4609,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>864</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4633,10 +4633,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>586424</v>
+        <v>586263</v>
       </c>
       <c r="R38" t="n">
-        <v>7274747</v>
+        <v>7274991</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4695,10 +4695,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121477319</v>
+        <v>121476597</v>
       </c>
       <c r="B39" t="n">
-        <v>78604</v>
+        <v>79689</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4711,21 +4711,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>586263</v>
+        <v>586361</v>
       </c>
       <c r="R39" t="n">
-        <v>7274991</v>
+        <v>7274887</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4797,10 +4797,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121477312</v>
+        <v>121477315</v>
       </c>
       <c r="B40" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4837,10 +4837,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>586774</v>
+        <v>586410</v>
       </c>
       <c r="R40" t="n">
-        <v>7274818</v>
+        <v>7274861</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4899,10 +4899,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121476688</v>
+        <v>121476595</v>
       </c>
       <c r="B41" t="n">
-        <v>90996</v>
+        <v>79689</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4915,21 +4915,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4939,10 +4939,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>586513</v>
+        <v>586410</v>
       </c>
       <c r="R41" t="n">
-        <v>7275037</v>
+        <v>7274861</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5001,10 +5001,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121476521</v>
+        <v>121477312</v>
       </c>
       <c r="B42" t="n">
-        <v>79551</v>
+        <v>78607</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5017,21 +5017,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>388</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5041,10 +5041,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>586320</v>
+        <v>586774</v>
       </c>
       <c r="R42" t="n">
-        <v>7274981</v>
+        <v>7274818</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5103,10 +5103,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121476718</v>
+        <v>121477385</v>
       </c>
       <c r="B43" t="n">
-        <v>79685</v>
+        <v>82391</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5119,21 +5119,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5143,10 +5143,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>586671</v>
+        <v>586263</v>
       </c>
       <c r="R43" t="n">
-        <v>7274637</v>
+        <v>7274991</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>

--- a/artfynd/A 31945-2021 artfynd.xlsx
+++ b/artfynd/A 31945-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY43"/>
+  <dimension ref="A1:AY60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3063,10 +3063,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121477395</v>
+        <v>121476595</v>
       </c>
       <c r="B23" t="n">
-        <v>88034</v>
+        <v>79689</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3079,21 +3079,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>510</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3103,10 +3103,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>586434</v>
+        <v>586410</v>
       </c>
       <c r="R23" t="n">
-        <v>7274787</v>
+        <v>7274861</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3165,10 +3165,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121476598</v>
+        <v>121476441</v>
       </c>
       <c r="B24" t="n">
-        <v>79689</v>
+        <v>90713</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3181,21 +3181,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3205,10 +3205,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>586242</v>
+        <v>586513</v>
       </c>
       <c r="R24" t="n">
-        <v>7274946</v>
+        <v>7275037</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3267,7 +3267,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121476441</v>
+        <v>121476439</v>
       </c>
       <c r="B25" t="n">
         <v>90713</v>
@@ -3307,10 +3307,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>586513</v>
+        <v>586310</v>
       </c>
       <c r="R25" t="n">
-        <v>7275037</v>
+        <v>7274979</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3369,10 +3369,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121476721</v>
+        <v>121477312</v>
       </c>
       <c r="B26" t="n">
-        <v>79688</v>
+        <v>78607</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3385,21 +3385,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3409,10 +3409,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>586434</v>
+        <v>586774</v>
       </c>
       <c r="R26" t="n">
-        <v>7274787</v>
+        <v>7274818</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3471,10 +3471,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121476846</v>
+        <v>121476521</v>
       </c>
       <c r="B27" t="n">
-        <v>90709</v>
+        <v>79554</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3487,21 +3487,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1108</v>
+        <v>388</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>586623</v>
+        <v>586320</v>
       </c>
       <c r="R27" t="n">
-        <v>7275057</v>
+        <v>7274981</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3573,10 +3573,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121476688</v>
+        <v>121476846</v>
       </c>
       <c r="B28" t="n">
-        <v>90999</v>
+        <v>90709</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3589,21 +3589,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>586513</v>
+        <v>586623</v>
       </c>
       <c r="R28" t="n">
-        <v>7275037</v>
+        <v>7275057</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3675,7 +3675,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121476719</v>
+        <v>121476718</v>
       </c>
       <c r="B29" t="n">
         <v>79688</v>
@@ -3715,10 +3715,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>586424</v>
+        <v>586671</v>
       </c>
       <c r="R29" t="n">
-        <v>7274747</v>
+        <v>7274637</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3777,10 +3777,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121476841</v>
+        <v>121476719</v>
       </c>
       <c r="B30" t="n">
-        <v>90709</v>
+        <v>79688</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3793,21 +3793,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3817,10 +3817,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>586739</v>
+        <v>586424</v>
       </c>
       <c r="R30" t="n">
-        <v>7274805</v>
+        <v>7274747</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3879,10 +3879,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121476718</v>
+        <v>121476600</v>
       </c>
       <c r="B31" t="n">
-        <v>79688</v>
+        <v>79689</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3895,21 +3895,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3919,10 +3919,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>586671</v>
+        <v>586290</v>
       </c>
       <c r="R31" t="n">
-        <v>7274637</v>
+        <v>7274978</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3981,10 +3981,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121476439</v>
+        <v>121477395</v>
       </c>
       <c r="B32" t="n">
-        <v>90713</v>
+        <v>88034</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3997,21 +3997,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4021,10 +4021,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>586310</v>
+        <v>586434</v>
       </c>
       <c r="R32" t="n">
-        <v>7274979</v>
+        <v>7274787</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4083,7 +4083,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121476600</v>
+        <v>121476597</v>
       </c>
       <c r="B33" t="n">
         <v>79689</v>
@@ -4123,10 +4123,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>586290</v>
+        <v>586361</v>
       </c>
       <c r="R33" t="n">
-        <v>7274978</v>
+        <v>7274887</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4185,10 +4185,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121477319</v>
+        <v>121476841</v>
       </c>
       <c r="B34" t="n">
-        <v>78607</v>
+        <v>90709</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4201,21 +4201,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4225,10 +4225,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>586263</v>
+        <v>586739</v>
       </c>
       <c r="R34" t="n">
-        <v>7274991</v>
+        <v>7274805</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4287,10 +4287,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121476521</v>
+        <v>121477385</v>
       </c>
       <c r="B35" t="n">
-        <v>79554</v>
+        <v>82391</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4303,21 +4303,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>388</v>
+        <v>1312</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4327,10 +4327,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>586320</v>
+        <v>586263</v>
       </c>
       <c r="R35" t="n">
-        <v>7274981</v>
+        <v>7274991</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4389,10 +4389,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121476843</v>
+        <v>121476598</v>
       </c>
       <c r="B36" t="n">
-        <v>90709</v>
+        <v>79689</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4405,21 +4405,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4429,10 +4429,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>586373</v>
+        <v>586242</v>
       </c>
       <c r="R36" t="n">
-        <v>7275002</v>
+        <v>7274946</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4491,10 +4491,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121476720</v>
+        <v>121477319</v>
       </c>
       <c r="B37" t="n">
-        <v>79688</v>
+        <v>78607</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4507,21 +4507,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4531,10 +4531,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>586428</v>
+        <v>586263</v>
       </c>
       <c r="R37" t="n">
-        <v>7274782</v>
+        <v>7274991</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4593,10 +4593,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121476790</v>
+        <v>121477315</v>
       </c>
       <c r="B38" t="n">
-        <v>78689</v>
+        <v>78607</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4609,21 +4609,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4633,10 +4633,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>586263</v>
+        <v>586410</v>
       </c>
       <c r="R38" t="n">
-        <v>7274991</v>
+        <v>7274861</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4695,10 +4695,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121476597</v>
+        <v>121476790</v>
       </c>
       <c r="B39" t="n">
-        <v>79689</v>
+        <v>78689</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4711,21 +4711,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>586361</v>
+        <v>586263</v>
       </c>
       <c r="R39" t="n">
-        <v>7274887</v>
+        <v>7274991</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4797,10 +4797,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121477315</v>
+        <v>121476721</v>
       </c>
       <c r="B40" t="n">
-        <v>78607</v>
+        <v>79688</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4813,21 +4813,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4837,10 +4837,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>586410</v>
+        <v>586434</v>
       </c>
       <c r="R40" t="n">
-        <v>7274861</v>
+        <v>7274787</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4899,10 +4899,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121476595</v>
+        <v>121476720</v>
       </c>
       <c r="B41" t="n">
-        <v>79689</v>
+        <v>79688</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4915,21 +4915,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4939,10 +4939,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>586410</v>
+        <v>586428</v>
       </c>
       <c r="R41" t="n">
-        <v>7274861</v>
+        <v>7274782</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5001,10 +5001,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121477312</v>
+        <v>121476688</v>
       </c>
       <c r="B42" t="n">
-        <v>78607</v>
+        <v>90999</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5017,21 +5017,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5041,10 +5041,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>586774</v>
+        <v>586513</v>
       </c>
       <c r="R42" t="n">
-        <v>7274818</v>
+        <v>7275037</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5103,10 +5103,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121477385</v>
+        <v>121476843</v>
       </c>
       <c r="B43" t="n">
-        <v>82391</v>
+        <v>90709</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5119,21 +5119,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5143,10 +5143,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>586263</v>
+        <v>586373</v>
       </c>
       <c r="R43" t="n">
-        <v>7274991</v>
+        <v>7275002</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5202,6 +5202,1978 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>121532535</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79688</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Sorsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>586434</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7274786</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>121532446</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79689</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Sorsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>586289</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7274978</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>121532577</v>
+      </c>
+      <c r="B46" t="n">
+        <v>78689</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>864</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Sorsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>586262</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7274991</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>121532632</v>
+      </c>
+      <c r="B47" t="n">
+        <v>90709</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Sorsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>586372</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7275002</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>121532443</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79689</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Sorsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>586360</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7274887</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>121533112</v>
+      </c>
+      <c r="B49" t="n">
+        <v>78607</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Sorsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>586773</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7274818</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>121532208</v>
+      </c>
+      <c r="B50" t="n">
+        <v>91275</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>760</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Doftticka</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Haploporus odorus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Sorsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>586434</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7274786</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>121532319</v>
+      </c>
+      <c r="B51" t="n">
+        <v>90713</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Sorsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>586310</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7274978</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>121532532</v>
+      </c>
+      <c r="B52" t="n">
+        <v>79688</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Sorsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>586670</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7274637</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>121532630</v>
+      </c>
+      <c r="B53" t="n">
+        <v>90709</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Sorsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>586738</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7274804</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>01:00</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>01:00</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>121532534</v>
+      </c>
+      <c r="B54" t="n">
+        <v>79688</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Sorsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>586428</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7274781</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>121532444</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79689</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Sorsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>586241</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7274946</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>121533115</v>
+      </c>
+      <c r="B56" t="n">
+        <v>78607</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Sorsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>586409</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7274860</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>121533188</v>
+      </c>
+      <c r="B57" t="n">
+        <v>82391</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Sorsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>586262</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7274991</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>121533119</v>
+      </c>
+      <c r="B58" t="n">
+        <v>78607</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Sorsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>586262</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7274991</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>121532442</v>
+      </c>
+      <c r="B59" t="n">
+        <v>79689</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Sorsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>586409</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7274860</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>121532533</v>
+      </c>
+      <c r="B60" t="n">
+        <v>79688</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Sorsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>586423</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7274746</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31945-2021 artfynd.xlsx
+++ b/artfynd/A 31945-2021 artfynd.xlsx
@@ -3573,10 +3573,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121476846</v>
+        <v>121476718</v>
       </c>
       <c r="B28" t="n">
-        <v>90709</v>
+        <v>79688</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3589,21 +3589,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>586623</v>
+        <v>586671</v>
       </c>
       <c r="R28" t="n">
-        <v>7275057</v>
+        <v>7274637</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3675,10 +3675,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121476718</v>
+        <v>121476846</v>
       </c>
       <c r="B29" t="n">
-        <v>79688</v>
+        <v>90709</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3691,21 +3691,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3715,10 +3715,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>586671</v>
+        <v>586623</v>
       </c>
       <c r="R29" t="n">
-        <v>7274637</v>
+        <v>7275057</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4593,10 +4593,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121477315</v>
+        <v>121476790</v>
       </c>
       <c r="B38" t="n">
-        <v>78607</v>
+        <v>78689</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4609,21 +4609,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4633,10 +4633,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>586410</v>
+        <v>586263</v>
       </c>
       <c r="R38" t="n">
-        <v>7274861</v>
+        <v>7274991</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4695,10 +4695,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121476790</v>
+        <v>121477315</v>
       </c>
       <c r="B39" t="n">
-        <v>78689</v>
+        <v>78607</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4711,21 +4711,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>586263</v>
+        <v>586410</v>
       </c>
       <c r="R39" t="n">
-        <v>7274991</v>
+        <v>7274861</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>

--- a/artfynd/A 31945-2021 artfynd.xlsx
+++ b/artfynd/A 31945-2021 artfynd.xlsx
@@ -3573,10 +3573,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121476718</v>
+        <v>121476846</v>
       </c>
       <c r="B28" t="n">
-        <v>79688</v>
+        <v>90709</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3589,21 +3589,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>586671</v>
+        <v>586623</v>
       </c>
       <c r="R28" t="n">
-        <v>7274637</v>
+        <v>7275057</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3675,10 +3675,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121476846</v>
+        <v>121476718</v>
       </c>
       <c r="B29" t="n">
-        <v>90709</v>
+        <v>79688</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3691,21 +3691,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3715,10 +3715,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>586623</v>
+        <v>586671</v>
       </c>
       <c r="R29" t="n">
-        <v>7275057</v>
+        <v>7274637</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4593,10 +4593,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121476790</v>
+        <v>121477315</v>
       </c>
       <c r="B38" t="n">
-        <v>78689</v>
+        <v>78607</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4609,21 +4609,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4633,10 +4633,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>586263</v>
+        <v>586410</v>
       </c>
       <c r="R38" t="n">
-        <v>7274991</v>
+        <v>7274861</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4695,10 +4695,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121477315</v>
+        <v>121476790</v>
       </c>
       <c r="B39" t="n">
-        <v>78607</v>
+        <v>78689</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4711,21 +4711,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>586410</v>
+        <v>586263</v>
       </c>
       <c r="R39" t="n">
-        <v>7274861</v>
+        <v>7274991</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -6713,10 +6713,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121533188</v>
+        <v>121532442</v>
       </c>
       <c r="B57" t="n">
-        <v>82391</v>
+        <v>79689</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6729,21 +6729,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1312</v>
+        <v>2081</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -6757,10 +6757,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>586262</v>
+        <v>586409</v>
       </c>
       <c r="R57" t="n">
-        <v>7274991</v>
+        <v>7274860</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6792,7 +6792,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6829,10 +6829,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121533119</v>
+        <v>121533188</v>
       </c>
       <c r="B58" t="n">
-        <v>78607</v>
+        <v>82391</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6845,21 +6845,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -6908,7 +6908,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6945,10 +6945,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121532442</v>
+        <v>121533119</v>
       </c>
       <c r="B59" t="n">
-        <v>79689</v>
+        <v>78607</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6961,21 +6961,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -6989,10 +6989,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>586409</v>
+        <v>586262</v>
       </c>
       <c r="R59" t="n">
-        <v>7274860</v>
+        <v>7274991</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7024,7 +7024,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AD59" t="b">

--- a/artfynd/A 31945-2021 artfynd.xlsx
+++ b/artfynd/A 31945-2021 artfynd.xlsx
@@ -3063,10 +3063,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121476595</v>
+        <v>121477385</v>
       </c>
       <c r="B23" t="n">
-        <v>79689</v>
+        <v>82392</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3079,21 +3079,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3103,10 +3103,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>586410</v>
+        <v>586263</v>
       </c>
       <c r="R23" t="n">
-        <v>7274861</v>
+        <v>7274991</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3168,7 +3168,7 @@
         <v>121476441</v>
       </c>
       <c r="B24" t="n">
-        <v>90713</v>
+        <v>90719</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3267,10 +3267,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121476439</v>
+        <v>121477312</v>
       </c>
       <c r="B25" t="n">
-        <v>90713</v>
+        <v>78608</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3283,21 +3283,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3307,10 +3307,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>586310</v>
+        <v>586774</v>
       </c>
       <c r="R25" t="n">
-        <v>7274979</v>
+        <v>7274818</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3369,10 +3369,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121477312</v>
+        <v>121476718</v>
       </c>
       <c r="B26" t="n">
-        <v>78607</v>
+        <v>79689</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3385,21 +3385,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3409,10 +3409,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>586774</v>
+        <v>586671</v>
       </c>
       <c r="R26" t="n">
-        <v>7274818</v>
+        <v>7274637</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3471,10 +3471,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121476521</v>
+        <v>121476720</v>
       </c>
       <c r="B27" t="n">
-        <v>79554</v>
+        <v>79689</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3487,21 +3487,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>388</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>586320</v>
+        <v>586428</v>
       </c>
       <c r="R27" t="n">
-        <v>7274981</v>
+        <v>7274782</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3573,10 +3573,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121476846</v>
+        <v>121476595</v>
       </c>
       <c r="B28" t="n">
-        <v>90709</v>
+        <v>79690</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3589,21 +3589,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>586623</v>
+        <v>586410</v>
       </c>
       <c r="R28" t="n">
-        <v>7275057</v>
+        <v>7274861</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3675,10 +3675,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121476718</v>
+        <v>121476598</v>
       </c>
       <c r="B29" t="n">
-        <v>79688</v>
+        <v>79690</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3691,21 +3691,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3715,10 +3715,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>586671</v>
+        <v>586242</v>
       </c>
       <c r="R29" t="n">
-        <v>7274637</v>
+        <v>7274946</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3780,7 +3780,7 @@
         <v>121476719</v>
       </c>
       <c r="B30" t="n">
-        <v>79688</v>
+        <v>79689</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3879,10 +3879,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121476600</v>
+        <v>121476843</v>
       </c>
       <c r="B31" t="n">
-        <v>79689</v>
+        <v>90715</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3895,21 +3895,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3919,10 +3919,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>586290</v>
+        <v>586373</v>
       </c>
       <c r="R31" t="n">
-        <v>7274978</v>
+        <v>7275002</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3984,7 +3984,7 @@
         <v>121477395</v>
       </c>
       <c r="B32" t="n">
-        <v>88034</v>
+        <v>88038</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4083,10 +4083,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121476597</v>
+        <v>121476439</v>
       </c>
       <c r="B33" t="n">
-        <v>79689</v>
+        <v>90719</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4099,21 +4099,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4123,10 +4123,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>586361</v>
+        <v>586310</v>
       </c>
       <c r="R33" t="n">
-        <v>7274887</v>
+        <v>7274979</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4185,10 +4185,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121476841</v>
+        <v>121476521</v>
       </c>
       <c r="B34" t="n">
-        <v>90709</v>
+        <v>79555</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4201,21 +4201,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1108</v>
+        <v>388</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4225,10 +4225,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>586739</v>
+        <v>586320</v>
       </c>
       <c r="R34" t="n">
-        <v>7274805</v>
+        <v>7274981</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4287,10 +4287,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121477385</v>
+        <v>121477315</v>
       </c>
       <c r="B35" t="n">
-        <v>82391</v>
+        <v>78608</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4303,21 +4303,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4327,10 +4327,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>586263</v>
+        <v>586410</v>
       </c>
       <c r="R35" t="n">
-        <v>7274991</v>
+        <v>7274861</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4389,10 +4389,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121476598</v>
+        <v>121476846</v>
       </c>
       <c r="B36" t="n">
-        <v>79689</v>
+        <v>90715</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4405,21 +4405,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4429,10 +4429,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>586242</v>
+        <v>586623</v>
       </c>
       <c r="R36" t="n">
-        <v>7274946</v>
+        <v>7275057</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4491,10 +4491,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121477319</v>
+        <v>121476721</v>
       </c>
       <c r="B37" t="n">
-        <v>78607</v>
+        <v>79689</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4507,21 +4507,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4531,10 +4531,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>586263</v>
+        <v>586434</v>
       </c>
       <c r="R37" t="n">
-        <v>7274991</v>
+        <v>7274787</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4593,10 +4593,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121477315</v>
+        <v>121476597</v>
       </c>
       <c r="B38" t="n">
-        <v>78607</v>
+        <v>79690</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4609,21 +4609,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4633,10 +4633,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>586410</v>
+        <v>586361</v>
       </c>
       <c r="R38" t="n">
-        <v>7274861</v>
+        <v>7274887</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4695,10 +4695,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121476790</v>
+        <v>121476600</v>
       </c>
       <c r="B39" t="n">
-        <v>78689</v>
+        <v>79690</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4711,21 +4711,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>586263</v>
+        <v>586290</v>
       </c>
       <c r="R39" t="n">
-        <v>7274991</v>
+        <v>7274978</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4797,10 +4797,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121476721</v>
+        <v>121476688</v>
       </c>
       <c r="B40" t="n">
-        <v>79688</v>
+        <v>91005</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4813,21 +4813,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4837,10 +4837,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>586434</v>
+        <v>586513</v>
       </c>
       <c r="R40" t="n">
-        <v>7274787</v>
+        <v>7275037</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4899,10 +4899,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121476720</v>
+        <v>121476790</v>
       </c>
       <c r="B41" t="n">
-        <v>79688</v>
+        <v>78690</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4915,21 +4915,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>864</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4939,10 +4939,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>586428</v>
+        <v>586263</v>
       </c>
       <c r="R41" t="n">
-        <v>7274782</v>
+        <v>7274991</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5001,10 +5001,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121476688</v>
+        <v>121477319</v>
       </c>
       <c r="B42" t="n">
-        <v>90999</v>
+        <v>78608</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5017,21 +5017,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5041,10 +5041,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>586513</v>
+        <v>586263</v>
       </c>
       <c r="R42" t="n">
-        <v>7275037</v>
+        <v>7274991</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5103,10 +5103,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121476843</v>
+        <v>121476841</v>
       </c>
       <c r="B43" t="n">
-        <v>90709</v>
+        <v>90715</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5143,10 +5143,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>586373</v>
+        <v>586739</v>
       </c>
       <c r="R43" t="n">
-        <v>7275002</v>
+        <v>7274805</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5205,10 +5205,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121532535</v>
+        <v>121532632</v>
       </c>
       <c r="B44" t="n">
-        <v>79688</v>
+        <v>90715</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5221,21 +5221,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5249,10 +5249,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>586434</v>
+        <v>586372</v>
       </c>
       <c r="R44" t="n">
-        <v>7274786</v>
+        <v>7275002</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5321,7 +5321,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121532446</v>
+        <v>121532533</v>
       </c>
       <c r="B45" t="n">
         <v>79689</v>
@@ -5337,21 +5337,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5365,10 +5365,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>586289</v>
+        <v>586423</v>
       </c>
       <c r="R45" t="n">
-        <v>7274978</v>
+        <v>7274746</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5400,7 +5400,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5410,7 +5410,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5437,10 +5437,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121532577</v>
+        <v>121533115</v>
       </c>
       <c r="B46" t="n">
-        <v>78689</v>
+        <v>78608</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5453,21 +5453,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5481,10 +5481,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>586262</v>
+        <v>586409</v>
       </c>
       <c r="R46" t="n">
-        <v>7274991</v>
+        <v>7274860</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5553,10 +5553,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121532632</v>
+        <v>121532446</v>
       </c>
       <c r="B47" t="n">
-        <v>90709</v>
+        <v>79690</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5569,21 +5569,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5597,10 +5597,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>586372</v>
+        <v>586289</v>
       </c>
       <c r="R47" t="n">
-        <v>7275002</v>
+        <v>7274978</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5632,7 +5632,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5642,7 +5642,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5669,7 +5669,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121532443</v>
+        <v>121532532</v>
       </c>
       <c r="B48" t="n">
         <v>79689</v>
@@ -5685,21 +5685,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5713,10 +5713,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>586360</v>
+        <v>586670</v>
       </c>
       <c r="R48" t="n">
-        <v>7274887</v>
+        <v>7274637</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5748,7 +5748,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5785,10 +5785,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121533112</v>
+        <v>121532535</v>
       </c>
       <c r="B49" t="n">
-        <v>78607</v>
+        <v>79689</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5801,21 +5801,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5829,10 +5829,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>586773</v>
+        <v>586434</v>
       </c>
       <c r="R49" t="n">
-        <v>7274818</v>
+        <v>7274786</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5864,7 +5864,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5874,7 +5874,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5901,10 +5901,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121532208</v>
+        <v>121532577</v>
       </c>
       <c r="B50" t="n">
-        <v>91275</v>
+        <v>78690</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5913,25 +5913,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>760</v>
+        <v>864</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5945,10 +5945,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>586434</v>
+        <v>586262</v>
       </c>
       <c r="R50" t="n">
-        <v>7274786</v>
+        <v>7274991</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5980,7 +5980,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5990,7 +5990,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6017,10 +6017,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121532319</v>
+        <v>121532534</v>
       </c>
       <c r="B51" t="n">
-        <v>90713</v>
+        <v>79689</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6033,21 +6033,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -6061,10 +6061,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>586310</v>
+        <v>586428</v>
       </c>
       <c r="R51" t="n">
-        <v>7274978</v>
+        <v>7274781</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6096,7 +6096,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6106,7 +6106,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6133,10 +6133,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121532532</v>
+        <v>121533112</v>
       </c>
       <c r="B52" t="n">
-        <v>79688</v>
+        <v>78608</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6149,21 +6149,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>586670</v>
+        <v>586773</v>
       </c>
       <c r="R52" t="n">
-        <v>7274637</v>
+        <v>7274818</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6212,7 +6212,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6249,10 +6249,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121532630</v>
+        <v>121532319</v>
       </c>
       <c r="B53" t="n">
-        <v>90709</v>
+        <v>90719</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6265,21 +6265,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -6293,10 +6293,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>586738</v>
+        <v>586310</v>
       </c>
       <c r="R53" t="n">
-        <v>7274804</v>
+        <v>7274978</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6328,7 +6328,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6338,7 +6338,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6365,10 +6365,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121532534</v>
+        <v>121533188</v>
       </c>
       <c r="B54" t="n">
-        <v>79688</v>
+        <v>82392</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6381,21 +6381,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -6409,10 +6409,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>586428</v>
+        <v>586262</v>
       </c>
       <c r="R54" t="n">
-        <v>7274781</v>
+        <v>7274991</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6481,10 +6481,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121532444</v>
+        <v>121532442</v>
       </c>
       <c r="B55" t="n">
-        <v>79689</v>
+        <v>79690</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6525,10 +6525,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>586241</v>
+        <v>586409</v>
       </c>
       <c r="R55" t="n">
-        <v>7274946</v>
+        <v>7274860</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6560,7 +6560,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6570,7 +6570,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6597,10 +6597,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121533115</v>
+        <v>121533119</v>
       </c>
       <c r="B56" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6641,10 +6641,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>586409</v>
+        <v>586262</v>
       </c>
       <c r="R56" t="n">
-        <v>7274860</v>
+        <v>7274991</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6676,7 +6676,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6686,7 +6686,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6713,10 +6713,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121532442</v>
+        <v>121532630</v>
       </c>
       <c r="B57" t="n">
-        <v>79689</v>
+        <v>90715</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6729,21 +6729,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -6757,10 +6757,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>586409</v>
+        <v>586738</v>
       </c>
       <c r="R57" t="n">
-        <v>7274860</v>
+        <v>7274804</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6792,7 +6792,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6829,10 +6829,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121533188</v>
+        <v>121532443</v>
       </c>
       <c r="B58" t="n">
-        <v>82391</v>
+        <v>79690</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6845,21 +6845,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1312</v>
+        <v>2081</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -6873,10 +6873,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>586262</v>
+        <v>586360</v>
       </c>
       <c r="R58" t="n">
-        <v>7274991</v>
+        <v>7274887</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6908,7 +6908,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6945,10 +6945,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121533119</v>
+        <v>121532444</v>
       </c>
       <c r="B59" t="n">
-        <v>78607</v>
+        <v>79690</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6961,21 +6961,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -6989,10 +6989,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>586262</v>
+        <v>586241</v>
       </c>
       <c r="R59" t="n">
-        <v>7274991</v>
+        <v>7274946</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7024,7 +7024,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7061,10 +7061,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121532533</v>
+        <v>121532208</v>
       </c>
       <c r="B60" t="n">
-        <v>79688</v>
+        <v>91281</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7073,25 +7073,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -7105,10 +7105,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>586423</v>
+        <v>586434</v>
       </c>
       <c r="R60" t="n">
-        <v>7274746</v>
+        <v>7274786</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7140,7 +7140,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7150,7 +7150,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD60" t="b">

--- a/artfynd/A 31945-2021 artfynd.xlsx
+++ b/artfynd/A 31945-2021 artfynd.xlsx
@@ -6133,10 +6133,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121533112</v>
+        <v>121532319</v>
       </c>
       <c r="B52" t="n">
-        <v>78608</v>
+        <v>90719</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6149,21 +6149,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>586773</v>
+        <v>586310</v>
       </c>
       <c r="R52" t="n">
-        <v>7274818</v>
+        <v>7274978</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6212,7 +6212,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6249,10 +6249,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121532319</v>
+        <v>121533112</v>
       </c>
       <c r="B53" t="n">
-        <v>90719</v>
+        <v>78608</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6265,21 +6265,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -6293,10 +6293,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>586310</v>
+        <v>586773</v>
       </c>
       <c r="R53" t="n">
-        <v>7274978</v>
+        <v>7274818</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6328,7 +6328,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6338,7 +6338,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6713,10 +6713,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121532630</v>
+        <v>121532208</v>
       </c>
       <c r="B57" t="n">
-        <v>90715</v>
+        <v>91281</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6725,25 +6725,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1108</v>
+        <v>760</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -6757,10 +6757,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>586738</v>
+        <v>586434</v>
       </c>
       <c r="R57" t="n">
-        <v>7274804</v>
+        <v>7274786</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6792,7 +6792,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6829,10 +6829,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121532443</v>
+        <v>121532630</v>
       </c>
       <c r="B58" t="n">
-        <v>79690</v>
+        <v>90715</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6845,21 +6845,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -6873,10 +6873,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>586360</v>
+        <v>586738</v>
       </c>
       <c r="R58" t="n">
-        <v>7274887</v>
+        <v>7274804</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6908,7 +6908,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6945,7 +6945,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121532444</v>
+        <v>121532443</v>
       </c>
       <c r="B59" t="n">
         <v>79690</v>
@@ -6989,10 +6989,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>586241</v>
+        <v>586360</v>
       </c>
       <c r="R59" t="n">
-        <v>7274946</v>
+        <v>7274887</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7024,7 +7024,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7061,10 +7061,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121532208</v>
+        <v>121532444</v>
       </c>
       <c r="B60" t="n">
-        <v>91281</v>
+        <v>79690</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7073,25 +7073,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>760</v>
+        <v>2081</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -7105,10 +7105,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>586434</v>
+        <v>586241</v>
       </c>
       <c r="R60" t="n">
-        <v>7274786</v>
+        <v>7274946</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7140,7 +7140,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7150,7 +7150,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD60" t="b">

--- a/artfynd/A 31945-2021 artfynd.xlsx
+++ b/artfynd/A 31945-2021 artfynd.xlsx
@@ -3063,10 +3063,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121477385</v>
+        <v>121476521</v>
       </c>
       <c r="B23" t="n">
-        <v>82392</v>
+        <v>79556</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3079,21 +3079,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>388</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3103,10 +3103,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>586263</v>
+        <v>586320</v>
       </c>
       <c r="R23" t="n">
-        <v>7274991</v>
+        <v>7274981</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3165,10 +3165,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121476441</v>
+        <v>121477312</v>
       </c>
       <c r="B24" t="n">
-        <v>90719</v>
+        <v>78609</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3181,21 +3181,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3205,10 +3205,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>586513</v>
+        <v>586774</v>
       </c>
       <c r="R24" t="n">
-        <v>7275037</v>
+        <v>7274818</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3267,10 +3267,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121477312</v>
+        <v>121476598</v>
       </c>
       <c r="B25" t="n">
-        <v>78608</v>
+        <v>79691</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3283,21 +3283,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3307,10 +3307,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>586774</v>
+        <v>586242</v>
       </c>
       <c r="R25" t="n">
-        <v>7274818</v>
+        <v>7274946</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3369,10 +3369,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121476718</v>
+        <v>121476790</v>
       </c>
       <c r="B26" t="n">
-        <v>79689</v>
+        <v>78691</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3385,21 +3385,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>864</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3409,10 +3409,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>586671</v>
+        <v>586263</v>
       </c>
       <c r="R26" t="n">
-        <v>7274637</v>
+        <v>7274991</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3474,7 +3474,7 @@
         <v>121476720</v>
       </c>
       <c r="B27" t="n">
-        <v>79689</v>
+        <v>79690</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121476595</v>
+        <v>121476718</v>
       </c>
       <c r="B28" t="n">
         <v>79690</v>
@@ -3589,21 +3589,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>586410</v>
+        <v>586671</v>
       </c>
       <c r="R28" t="n">
-        <v>7274861</v>
+        <v>7274637</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3675,10 +3675,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121476598</v>
+        <v>121476597</v>
       </c>
       <c r="B29" t="n">
-        <v>79690</v>
+        <v>79691</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3715,10 +3715,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>586242</v>
+        <v>586361</v>
       </c>
       <c r="R29" t="n">
-        <v>7274946</v>
+        <v>7274887</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3777,10 +3777,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121476719</v>
+        <v>121476721</v>
       </c>
       <c r="B30" t="n">
-        <v>79689</v>
+        <v>79690</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3817,10 +3817,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>586424</v>
+        <v>586434</v>
       </c>
       <c r="R30" t="n">
-        <v>7274747</v>
+        <v>7274787</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3879,10 +3879,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121476843</v>
+        <v>121476841</v>
       </c>
       <c r="B31" t="n">
-        <v>90715</v>
+        <v>90716</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3919,10 +3919,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>586373</v>
+        <v>586739</v>
       </c>
       <c r="R31" t="n">
-        <v>7275002</v>
+        <v>7274805</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3981,10 +3981,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121477395</v>
+        <v>121477315</v>
       </c>
       <c r="B32" t="n">
-        <v>88038</v>
+        <v>78609</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3997,21 +3997,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4021,10 +4021,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>586434</v>
+        <v>586410</v>
       </c>
       <c r="R32" t="n">
-        <v>7274787</v>
+        <v>7274861</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4086,7 +4086,7 @@
         <v>121476439</v>
       </c>
       <c r="B33" t="n">
-        <v>90719</v>
+        <v>90720</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4185,10 +4185,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121476521</v>
+        <v>121477319</v>
       </c>
       <c r="B34" t="n">
-        <v>79555</v>
+        <v>78609</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4201,21 +4201,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>388</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4225,10 +4225,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>586320</v>
+        <v>586263</v>
       </c>
       <c r="R34" t="n">
-        <v>7274981</v>
+        <v>7274991</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4287,10 +4287,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121477315</v>
+        <v>121476719</v>
       </c>
       <c r="B35" t="n">
-        <v>78608</v>
+        <v>79690</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4303,21 +4303,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4327,10 +4327,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>586410</v>
+        <v>586424</v>
       </c>
       <c r="R35" t="n">
-        <v>7274861</v>
+        <v>7274747</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4389,10 +4389,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121476846</v>
+        <v>121476441</v>
       </c>
       <c r="B36" t="n">
-        <v>90715</v>
+        <v>90720</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4405,21 +4405,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4429,10 +4429,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>586623</v>
+        <v>586513</v>
       </c>
       <c r="R36" t="n">
-        <v>7275057</v>
+        <v>7275037</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4491,10 +4491,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121476721</v>
+        <v>121476846</v>
       </c>
       <c r="B37" t="n">
-        <v>79689</v>
+        <v>90716</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4507,21 +4507,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4531,10 +4531,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>586434</v>
+        <v>586623</v>
       </c>
       <c r="R37" t="n">
-        <v>7274787</v>
+        <v>7275057</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4593,10 +4593,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121476597</v>
+        <v>121476600</v>
       </c>
       <c r="B38" t="n">
-        <v>79690</v>
+        <v>79691</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4633,10 +4633,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>586361</v>
+        <v>586290</v>
       </c>
       <c r="R38" t="n">
-        <v>7274887</v>
+        <v>7274978</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4695,10 +4695,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121476600</v>
+        <v>121476688</v>
       </c>
       <c r="B39" t="n">
-        <v>79690</v>
+        <v>91006</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4711,21 +4711,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>586290</v>
+        <v>586513</v>
       </c>
       <c r="R39" t="n">
-        <v>7274978</v>
+        <v>7275037</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4797,10 +4797,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121476688</v>
+        <v>121477395</v>
       </c>
       <c r="B40" t="n">
-        <v>91005</v>
+        <v>88039</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4813,21 +4813,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>510</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4837,10 +4837,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>586513</v>
+        <v>586434</v>
       </c>
       <c r="R40" t="n">
-        <v>7275037</v>
+        <v>7274787</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4899,10 +4899,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121476790</v>
+        <v>121476595</v>
       </c>
       <c r="B41" t="n">
-        <v>78690</v>
+        <v>79691</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4915,21 +4915,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4939,10 +4939,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>586263</v>
+        <v>586410</v>
       </c>
       <c r="R41" t="n">
-        <v>7274991</v>
+        <v>7274861</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5001,10 +5001,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121477319</v>
+        <v>121477385</v>
       </c>
       <c r="B42" t="n">
-        <v>78608</v>
+        <v>82393</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5017,21 +5017,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5103,10 +5103,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121476841</v>
+        <v>121476843</v>
       </c>
       <c r="B43" t="n">
-        <v>90715</v>
+        <v>90716</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5143,10 +5143,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>586739</v>
+        <v>586373</v>
       </c>
       <c r="R43" t="n">
-        <v>7274805</v>
+        <v>7275002</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5205,10 +5205,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121532632</v>
+        <v>121532577</v>
       </c>
       <c r="B44" t="n">
-        <v>90715</v>
+        <v>78691</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5221,21 +5221,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1108</v>
+        <v>864</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5249,10 +5249,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>586372</v>
+        <v>586262</v>
       </c>
       <c r="R44" t="n">
-        <v>7275002</v>
+        <v>7274991</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5321,10 +5321,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121532533</v>
+        <v>121532535</v>
       </c>
       <c r="B45" t="n">
-        <v>79689</v>
+        <v>79690</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5365,10 +5365,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>586423</v>
+        <v>586434</v>
       </c>
       <c r="R45" t="n">
-        <v>7274746</v>
+        <v>7274786</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5400,7 +5400,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5410,7 +5410,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5437,10 +5437,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121533115</v>
+        <v>121532444</v>
       </c>
       <c r="B46" t="n">
-        <v>78608</v>
+        <v>79691</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5453,21 +5453,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5481,10 +5481,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>586409</v>
+        <v>586241</v>
       </c>
       <c r="R46" t="n">
-        <v>7274860</v>
+        <v>7274946</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5553,10 +5553,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121532446</v>
+        <v>121532208</v>
       </c>
       <c r="B47" t="n">
-        <v>79690</v>
+        <v>91282</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5565,25 +5565,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2081</v>
+        <v>760</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5597,10 +5597,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>586289</v>
+        <v>586434</v>
       </c>
       <c r="R47" t="n">
-        <v>7274978</v>
+        <v>7274786</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5632,7 +5632,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5642,7 +5642,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5669,10 +5669,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121532532</v>
+        <v>121532446</v>
       </c>
       <c r="B48" t="n">
-        <v>79689</v>
+        <v>79691</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5685,21 +5685,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5713,10 +5713,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>586670</v>
+        <v>586289</v>
       </c>
       <c r="R48" t="n">
-        <v>7274637</v>
+        <v>7274978</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5748,7 +5748,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5785,10 +5785,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121532535</v>
+        <v>121532632</v>
       </c>
       <c r="B49" t="n">
-        <v>79689</v>
+        <v>90716</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5801,21 +5801,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5829,10 +5829,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>586434</v>
+        <v>586372</v>
       </c>
       <c r="R49" t="n">
-        <v>7274786</v>
+        <v>7275002</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5864,7 +5864,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5874,7 +5874,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5901,10 +5901,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121532577</v>
+        <v>121532443</v>
       </c>
       <c r="B50" t="n">
-        <v>78690</v>
+        <v>79691</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5917,21 +5917,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5945,10 +5945,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>586262</v>
+        <v>586360</v>
       </c>
       <c r="R50" t="n">
-        <v>7274991</v>
+        <v>7274887</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5980,7 +5980,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5990,7 +5990,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6017,10 +6017,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121532534</v>
+        <v>121532319</v>
       </c>
       <c r="B51" t="n">
-        <v>79689</v>
+        <v>90720</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6033,21 +6033,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -6061,10 +6061,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>586428</v>
+        <v>586310</v>
       </c>
       <c r="R51" t="n">
-        <v>7274781</v>
+        <v>7274978</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6096,7 +6096,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6106,7 +6106,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6133,10 +6133,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121532319</v>
+        <v>121533188</v>
       </c>
       <c r="B52" t="n">
-        <v>90719</v>
+        <v>82393</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6149,21 +6149,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>586310</v>
+        <v>586262</v>
       </c>
       <c r="R52" t="n">
-        <v>7274978</v>
+        <v>7274991</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6212,7 +6212,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6249,10 +6249,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121533112</v>
+        <v>121533119</v>
       </c>
       <c r="B53" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6293,10 +6293,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>586773</v>
+        <v>586262</v>
       </c>
       <c r="R53" t="n">
-        <v>7274818</v>
+        <v>7274991</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6328,7 +6328,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6338,7 +6338,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6365,10 +6365,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121533188</v>
+        <v>121532630</v>
       </c>
       <c r="B54" t="n">
-        <v>82392</v>
+        <v>90716</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6381,21 +6381,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -6409,10 +6409,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>586262</v>
+        <v>586738</v>
       </c>
       <c r="R54" t="n">
-        <v>7274991</v>
+        <v>7274804</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6481,7 +6481,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121532442</v>
+        <v>121532534</v>
       </c>
       <c r="B55" t="n">
         <v>79690</v>
@@ -6497,21 +6497,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -6525,10 +6525,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>586409</v>
+        <v>586428</v>
       </c>
       <c r="R55" t="n">
-        <v>7274860</v>
+        <v>7274781</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6560,7 +6560,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6570,7 +6570,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6597,10 +6597,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121533119</v>
+        <v>121532442</v>
       </c>
       <c r="B56" t="n">
-        <v>78608</v>
+        <v>79691</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6613,21 +6613,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -6641,10 +6641,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>586262</v>
+        <v>586409</v>
       </c>
       <c r="R56" t="n">
-        <v>7274991</v>
+        <v>7274860</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6676,7 +6676,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6686,7 +6686,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6713,10 +6713,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121532208</v>
+        <v>121532533</v>
       </c>
       <c r="B57" t="n">
-        <v>91281</v>
+        <v>79690</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6725,25 +6725,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -6757,10 +6757,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>586434</v>
+        <v>586423</v>
       </c>
       <c r="R57" t="n">
-        <v>7274786</v>
+        <v>7274746</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6792,7 +6792,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6829,10 +6829,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121532630</v>
+        <v>121532532</v>
       </c>
       <c r="B58" t="n">
-        <v>90715</v>
+        <v>79690</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6845,21 +6845,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -6873,10 +6873,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>586738</v>
+        <v>586670</v>
       </c>
       <c r="R58" t="n">
-        <v>7274804</v>
+        <v>7274637</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6908,7 +6908,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6945,10 +6945,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121532443</v>
+        <v>121533115</v>
       </c>
       <c r="B59" t="n">
-        <v>79690</v>
+        <v>78609</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6961,21 +6961,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -6989,10 +6989,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>586360</v>
+        <v>586409</v>
       </c>
       <c r="R59" t="n">
-        <v>7274887</v>
+        <v>7274860</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7024,7 +7024,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7061,10 +7061,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121532444</v>
+        <v>121533112</v>
       </c>
       <c r="B60" t="n">
-        <v>79690</v>
+        <v>78609</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7077,21 +7077,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -7105,10 +7105,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>586241</v>
+        <v>586773</v>
       </c>
       <c r="R60" t="n">
-        <v>7274946</v>
+        <v>7274818</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7140,7 +7140,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7150,7 +7150,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="AD60" t="b">

--- a/artfynd/A 31945-2021 artfynd.xlsx
+++ b/artfynd/A 31945-2021 artfynd.xlsx
@@ -3063,10 +3063,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121476521</v>
+        <v>121476721</v>
       </c>
       <c r="B23" t="n">
-        <v>79556</v>
+        <v>79690</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3079,21 +3079,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>388</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3103,10 +3103,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>586320</v>
+        <v>586434</v>
       </c>
       <c r="R23" t="n">
-        <v>7274981</v>
+        <v>7274787</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3165,10 +3165,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121477312</v>
+        <v>121476718</v>
       </c>
       <c r="B24" t="n">
-        <v>78609</v>
+        <v>79690</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3181,21 +3181,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3205,10 +3205,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>586774</v>
+        <v>586671</v>
       </c>
       <c r="R24" t="n">
-        <v>7274818</v>
+        <v>7274637</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3267,10 +3267,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121476598</v>
+        <v>121477319</v>
       </c>
       <c r="B25" t="n">
-        <v>79691</v>
+        <v>78609</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3283,21 +3283,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3307,10 +3307,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>586242</v>
+        <v>586263</v>
       </c>
       <c r="R25" t="n">
-        <v>7274946</v>
+        <v>7274991</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3369,10 +3369,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121476790</v>
+        <v>121476688</v>
       </c>
       <c r="B26" t="n">
-        <v>78691</v>
+        <v>91006</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3385,21 +3385,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>864</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3409,10 +3409,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>586263</v>
+        <v>586513</v>
       </c>
       <c r="R26" t="n">
-        <v>7274991</v>
+        <v>7275037</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3471,10 +3471,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121476720</v>
+        <v>121476598</v>
       </c>
       <c r="B27" t="n">
-        <v>79690</v>
+        <v>79691</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3487,21 +3487,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>586428</v>
+        <v>586242</v>
       </c>
       <c r="R27" t="n">
-        <v>7274782</v>
+        <v>7274946</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3573,7 +3573,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121476718</v>
+        <v>121476720</v>
       </c>
       <c r="B28" t="n">
         <v>79690</v>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>586671</v>
+        <v>586428</v>
       </c>
       <c r="R28" t="n">
-        <v>7274637</v>
+        <v>7274782</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3675,10 +3675,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121476597</v>
+        <v>121476521</v>
       </c>
       <c r="B29" t="n">
-        <v>79691</v>
+        <v>79556</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3691,21 +3691,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>388</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3715,10 +3715,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>586361</v>
+        <v>586320</v>
       </c>
       <c r="R29" t="n">
-        <v>7274887</v>
+        <v>7274981</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3777,10 +3777,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121476721</v>
+        <v>121476841</v>
       </c>
       <c r="B30" t="n">
-        <v>79690</v>
+        <v>90716</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3793,21 +3793,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3817,10 +3817,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>586434</v>
+        <v>586739</v>
       </c>
       <c r="R30" t="n">
-        <v>7274787</v>
+        <v>7274805</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3879,10 +3879,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121476841</v>
+        <v>121476790</v>
       </c>
       <c r="B31" t="n">
-        <v>90716</v>
+        <v>78691</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3895,21 +3895,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1108</v>
+        <v>864</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3919,10 +3919,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>586739</v>
+        <v>586263</v>
       </c>
       <c r="R31" t="n">
-        <v>7274805</v>
+        <v>7274991</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3981,10 +3981,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121477315</v>
+        <v>121476441</v>
       </c>
       <c r="B32" t="n">
-        <v>78609</v>
+        <v>90720</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3997,21 +3997,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4021,10 +4021,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>586410</v>
+        <v>586513</v>
       </c>
       <c r="R32" t="n">
-        <v>7274861</v>
+        <v>7275037</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4083,10 +4083,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121476439</v>
+        <v>121476595</v>
       </c>
       <c r="B33" t="n">
-        <v>90720</v>
+        <v>79691</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4099,21 +4099,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4123,10 +4123,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>586310</v>
+        <v>586410</v>
       </c>
       <c r="R33" t="n">
-        <v>7274979</v>
+        <v>7274861</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4185,7 +4185,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121477319</v>
+        <v>121477315</v>
       </c>
       <c r="B34" t="n">
         <v>78609</v>
@@ -4225,10 +4225,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>586263</v>
+        <v>586410</v>
       </c>
       <c r="R34" t="n">
-        <v>7274991</v>
+        <v>7274861</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4287,10 +4287,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121476719</v>
+        <v>121477312</v>
       </c>
       <c r="B35" t="n">
-        <v>79690</v>
+        <v>78609</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4303,21 +4303,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4327,10 +4327,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>586424</v>
+        <v>586774</v>
       </c>
       <c r="R35" t="n">
-        <v>7274747</v>
+        <v>7274818</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4389,10 +4389,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121476441</v>
+        <v>121477395</v>
       </c>
       <c r="B36" t="n">
-        <v>90720</v>
+        <v>88039</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4405,21 +4405,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4429,10 +4429,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>586513</v>
+        <v>586434</v>
       </c>
       <c r="R36" t="n">
-        <v>7275037</v>
+        <v>7274787</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4491,7 +4491,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121476846</v>
+        <v>121476843</v>
       </c>
       <c r="B37" t="n">
         <v>90716</v>
@@ -4531,10 +4531,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>586623</v>
+        <v>586373</v>
       </c>
       <c r="R37" t="n">
-        <v>7275057</v>
+        <v>7275002</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4695,10 +4695,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121476688</v>
+        <v>121476439</v>
       </c>
       <c r="B39" t="n">
-        <v>91006</v>
+        <v>90720</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4711,21 +4711,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>586513</v>
+        <v>586310</v>
       </c>
       <c r="R39" t="n">
-        <v>7275037</v>
+        <v>7274979</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4797,10 +4797,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121477395</v>
+        <v>121476846</v>
       </c>
       <c r="B40" t="n">
-        <v>88039</v>
+        <v>90716</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4813,21 +4813,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>510</v>
+        <v>1108</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4837,10 +4837,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>586434</v>
+        <v>586623</v>
       </c>
       <c r="R40" t="n">
-        <v>7274787</v>
+        <v>7275057</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4899,7 +4899,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121476595</v>
+        <v>121476597</v>
       </c>
       <c r="B41" t="n">
         <v>79691</v>
@@ -4939,10 +4939,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>586410</v>
+        <v>586361</v>
       </c>
       <c r="R41" t="n">
-        <v>7274861</v>
+        <v>7274887</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5001,10 +5001,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121477385</v>
+        <v>121476719</v>
       </c>
       <c r="B42" t="n">
-        <v>82393</v>
+        <v>79690</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5017,21 +5017,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5041,10 +5041,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>586263</v>
+        <v>586424</v>
       </c>
       <c r="R42" t="n">
-        <v>7274991</v>
+        <v>7274747</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5103,10 +5103,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121476843</v>
+        <v>121477385</v>
       </c>
       <c r="B43" t="n">
-        <v>90716</v>
+        <v>82393</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5119,21 +5119,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5143,10 +5143,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>586373</v>
+        <v>586263</v>
       </c>
       <c r="R43" t="n">
-        <v>7275002</v>
+        <v>7274991</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5205,10 +5205,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121532577</v>
+        <v>121532532</v>
       </c>
       <c r="B44" t="n">
-        <v>78691</v>
+        <v>79690</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5221,21 +5221,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>864</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5249,10 +5249,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>586262</v>
+        <v>586670</v>
       </c>
       <c r="R44" t="n">
-        <v>7274991</v>
+        <v>7274637</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5321,10 +5321,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121532535</v>
+        <v>121532443</v>
       </c>
       <c r="B45" t="n">
-        <v>79690</v>
+        <v>79691</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5337,21 +5337,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5365,10 +5365,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>586434</v>
+        <v>586360</v>
       </c>
       <c r="R45" t="n">
-        <v>7274786</v>
+        <v>7274887</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5400,7 +5400,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5410,7 +5410,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5553,10 +5553,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121532208</v>
+        <v>121533119</v>
       </c>
       <c r="B47" t="n">
-        <v>91282</v>
+        <v>78609</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5565,25 +5565,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5597,10 +5597,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>586434</v>
+        <v>586262</v>
       </c>
       <c r="R47" t="n">
-        <v>7274786</v>
+        <v>7274991</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5632,7 +5632,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5642,7 +5642,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5669,10 +5669,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121532446</v>
+        <v>121532535</v>
       </c>
       <c r="B48" t="n">
-        <v>79691</v>
+        <v>79690</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5685,21 +5685,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5713,10 +5713,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>586289</v>
+        <v>586434</v>
       </c>
       <c r="R48" t="n">
-        <v>7274978</v>
+        <v>7274786</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5748,7 +5748,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5785,10 +5785,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121532632</v>
+        <v>121533115</v>
       </c>
       <c r="B49" t="n">
-        <v>90716</v>
+        <v>78609</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5801,21 +5801,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5829,10 +5829,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>586372</v>
+        <v>586409</v>
       </c>
       <c r="R49" t="n">
-        <v>7275002</v>
+        <v>7274860</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5864,7 +5864,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5874,7 +5874,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5901,7 +5901,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121532443</v>
+        <v>121532446</v>
       </c>
       <c r="B50" t="n">
         <v>79691</v>
@@ -5945,10 +5945,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>586360</v>
+        <v>586289</v>
       </c>
       <c r="R50" t="n">
-        <v>7274887</v>
+        <v>7274978</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5980,7 +5980,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5990,7 +5990,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6017,10 +6017,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121532319</v>
+        <v>121532534</v>
       </c>
       <c r="B51" t="n">
-        <v>90720</v>
+        <v>79690</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6033,21 +6033,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -6061,10 +6061,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>586310</v>
+        <v>586428</v>
       </c>
       <c r="R51" t="n">
-        <v>7274978</v>
+        <v>7274781</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6096,7 +6096,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6106,7 +6106,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6133,10 +6133,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121533188</v>
+        <v>121533112</v>
       </c>
       <c r="B52" t="n">
-        <v>82393</v>
+        <v>78609</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6149,21 +6149,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>586262</v>
+        <v>586773</v>
       </c>
       <c r="R52" t="n">
-        <v>7274991</v>
+        <v>7274818</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6212,7 +6212,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6249,10 +6249,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121533119</v>
+        <v>121533188</v>
       </c>
       <c r="B53" t="n">
-        <v>78609</v>
+        <v>82393</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6265,21 +6265,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6338,7 +6338,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6365,10 +6365,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121532630</v>
+        <v>121532577</v>
       </c>
       <c r="B54" t="n">
-        <v>90716</v>
+        <v>78691</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6381,21 +6381,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1108</v>
+        <v>864</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -6409,10 +6409,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>586738</v>
+        <v>586262</v>
       </c>
       <c r="R54" t="n">
-        <v>7274804</v>
+        <v>7274991</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6481,10 +6481,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121532534</v>
+        <v>121532319</v>
       </c>
       <c r="B55" t="n">
-        <v>79690</v>
+        <v>90720</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6497,21 +6497,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -6525,10 +6525,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>586428</v>
+        <v>586310</v>
       </c>
       <c r="R55" t="n">
-        <v>7274781</v>
+        <v>7274978</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6560,7 +6560,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6570,7 +6570,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6713,10 +6713,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121532533</v>
+        <v>121532632</v>
       </c>
       <c r="B57" t="n">
-        <v>79690</v>
+        <v>90716</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6729,21 +6729,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -6757,10 +6757,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>586423</v>
+        <v>586372</v>
       </c>
       <c r="R57" t="n">
-        <v>7274746</v>
+        <v>7275002</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6792,7 +6792,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6829,7 +6829,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121532532</v>
+        <v>121532533</v>
       </c>
       <c r="B58" t="n">
         <v>79690</v>
@@ -6873,10 +6873,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>586670</v>
+        <v>586423</v>
       </c>
       <c r="R58" t="n">
-        <v>7274637</v>
+        <v>7274746</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6908,7 +6908,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6945,10 +6945,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121533115</v>
+        <v>121532630</v>
       </c>
       <c r="B59" t="n">
-        <v>78609</v>
+        <v>90716</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6961,21 +6961,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -6989,10 +6989,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>586409</v>
+        <v>586738</v>
       </c>
       <c r="R59" t="n">
-        <v>7274860</v>
+        <v>7274804</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7024,7 +7024,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7061,10 +7061,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121533112</v>
+        <v>121532208</v>
       </c>
       <c r="B60" t="n">
-        <v>78609</v>
+        <v>91282</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7073,25 +7073,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -7105,10 +7105,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>586773</v>
+        <v>586434</v>
       </c>
       <c r="R60" t="n">
-        <v>7274818</v>
+        <v>7274786</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7140,7 +7140,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7150,7 +7150,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD60" t="b">

--- a/artfynd/A 31945-2021 artfynd.xlsx
+++ b/artfynd/A 31945-2021 artfynd.xlsx
@@ -3063,10 +3063,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121476721</v>
+        <v>121476597</v>
       </c>
       <c r="B23" t="n">
-        <v>79690</v>
+        <v>79691</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3079,21 +3079,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3103,10 +3103,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>586434</v>
+        <v>586361</v>
       </c>
       <c r="R23" t="n">
-        <v>7274787</v>
+        <v>7274887</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3165,10 +3165,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121476718</v>
+        <v>121476441</v>
       </c>
       <c r="B24" t="n">
-        <v>79690</v>
+        <v>90720</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3181,21 +3181,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3205,10 +3205,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>586671</v>
+        <v>586513</v>
       </c>
       <c r="R24" t="n">
-        <v>7274637</v>
+        <v>7275037</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3267,7 +3267,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121477319</v>
+        <v>121477312</v>
       </c>
       <c r="B25" t="n">
         <v>78609</v>
@@ -3307,10 +3307,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>586263</v>
+        <v>586774</v>
       </c>
       <c r="R25" t="n">
-        <v>7274991</v>
+        <v>7274818</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3369,10 +3369,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121476688</v>
+        <v>121477315</v>
       </c>
       <c r="B26" t="n">
-        <v>91006</v>
+        <v>78609</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3385,21 +3385,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3409,10 +3409,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>586513</v>
+        <v>586410</v>
       </c>
       <c r="R26" t="n">
-        <v>7275037</v>
+        <v>7274861</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3471,10 +3471,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121476598</v>
+        <v>121476841</v>
       </c>
       <c r="B27" t="n">
-        <v>79691</v>
+        <v>90716</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3487,21 +3487,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>586242</v>
+        <v>586739</v>
       </c>
       <c r="R27" t="n">
-        <v>7274946</v>
+        <v>7274805</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3573,7 +3573,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121476720</v>
+        <v>121476721</v>
       </c>
       <c r="B28" t="n">
         <v>79690</v>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>586428</v>
+        <v>586434</v>
       </c>
       <c r="R28" t="n">
-        <v>7274782</v>
+        <v>7274787</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3675,10 +3675,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121476521</v>
+        <v>121476439</v>
       </c>
       <c r="B29" t="n">
-        <v>79556</v>
+        <v>90720</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3691,21 +3691,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>388</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3715,10 +3715,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>586320</v>
+        <v>586310</v>
       </c>
       <c r="R29" t="n">
-        <v>7274981</v>
+        <v>7274979</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3777,10 +3777,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121476841</v>
+        <v>121476718</v>
       </c>
       <c r="B30" t="n">
-        <v>90716</v>
+        <v>79690</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3793,21 +3793,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3817,10 +3817,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>586739</v>
+        <v>586671</v>
       </c>
       <c r="R30" t="n">
-        <v>7274805</v>
+        <v>7274637</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3879,10 +3879,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121476790</v>
+        <v>121476719</v>
       </c>
       <c r="B31" t="n">
-        <v>78691</v>
+        <v>79690</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3895,21 +3895,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>864</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3919,10 +3919,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>586263</v>
+        <v>586424</v>
       </c>
       <c r="R31" t="n">
-        <v>7274991</v>
+        <v>7274747</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3981,10 +3981,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121476441</v>
+        <v>121476688</v>
       </c>
       <c r="B32" t="n">
-        <v>90720</v>
+        <v>91006</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3997,21 +3997,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4083,10 +4083,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121476595</v>
+        <v>121477319</v>
       </c>
       <c r="B33" t="n">
-        <v>79691</v>
+        <v>78609</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4099,21 +4099,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4123,10 +4123,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>586410</v>
+        <v>586263</v>
       </c>
       <c r="R33" t="n">
-        <v>7274861</v>
+        <v>7274991</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4185,10 +4185,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121477315</v>
+        <v>121476595</v>
       </c>
       <c r="B34" t="n">
-        <v>78609</v>
+        <v>79691</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4201,21 +4201,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4287,10 +4287,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121477312</v>
+        <v>121476843</v>
       </c>
       <c r="B35" t="n">
-        <v>78609</v>
+        <v>90716</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4303,21 +4303,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4327,10 +4327,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>586774</v>
+        <v>586373</v>
       </c>
       <c r="R35" t="n">
-        <v>7274818</v>
+        <v>7275002</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4389,10 +4389,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121477395</v>
+        <v>121477385</v>
       </c>
       <c r="B36" t="n">
-        <v>88039</v>
+        <v>82393</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4405,21 +4405,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>510</v>
+        <v>1312</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4429,10 +4429,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>586434</v>
+        <v>586263</v>
       </c>
       <c r="R36" t="n">
-        <v>7274787</v>
+        <v>7274991</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4491,10 +4491,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121476843</v>
+        <v>121476598</v>
       </c>
       <c r="B37" t="n">
-        <v>90716</v>
+        <v>79691</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4507,21 +4507,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4531,10 +4531,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>586373</v>
+        <v>586242</v>
       </c>
       <c r="R37" t="n">
-        <v>7275002</v>
+        <v>7274946</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4695,10 +4695,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121476439</v>
+        <v>121476846</v>
       </c>
       <c r="B39" t="n">
-        <v>90720</v>
+        <v>90716</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4711,21 +4711,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>586310</v>
+        <v>586623</v>
       </c>
       <c r="R39" t="n">
-        <v>7274979</v>
+        <v>7275057</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4797,10 +4797,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121476846</v>
+        <v>121477395</v>
       </c>
       <c r="B40" t="n">
-        <v>90716</v>
+        <v>88039</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4813,21 +4813,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1108</v>
+        <v>510</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4837,10 +4837,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>586623</v>
+        <v>586434</v>
       </c>
       <c r="R40" t="n">
-        <v>7275057</v>
+        <v>7274787</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4899,10 +4899,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121476597</v>
+        <v>121476720</v>
       </c>
       <c r="B41" t="n">
-        <v>79691</v>
+        <v>79690</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4915,21 +4915,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4939,10 +4939,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>586361</v>
+        <v>586428</v>
       </c>
       <c r="R41" t="n">
-        <v>7274887</v>
+        <v>7274782</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5001,10 +5001,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121476719</v>
+        <v>121476521</v>
       </c>
       <c r="B42" t="n">
-        <v>79690</v>
+        <v>79556</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5017,21 +5017,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>388</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5041,10 +5041,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>586424</v>
+        <v>586320</v>
       </c>
       <c r="R42" t="n">
-        <v>7274747</v>
+        <v>7274981</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5103,10 +5103,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121477385</v>
+        <v>121476790</v>
       </c>
       <c r="B43" t="n">
-        <v>82393</v>
+        <v>78691</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5119,21 +5119,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5205,10 +5205,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121532532</v>
+        <v>121532446</v>
       </c>
       <c r="B44" t="n">
-        <v>79690</v>
+        <v>79691</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5221,21 +5221,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5249,10 +5249,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>586670</v>
+        <v>586289</v>
       </c>
       <c r="R44" t="n">
-        <v>7274637</v>
+        <v>7274978</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5321,7 +5321,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121532443</v>
+        <v>121532442</v>
       </c>
       <c r="B45" t="n">
         <v>79691</v>
@@ -5365,10 +5365,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>586360</v>
+        <v>586409</v>
       </c>
       <c r="R45" t="n">
-        <v>7274887</v>
+        <v>7274860</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5400,7 +5400,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5410,7 +5410,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5437,10 +5437,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121532444</v>
+        <v>121532535</v>
       </c>
       <c r="B46" t="n">
-        <v>79691</v>
+        <v>79690</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5453,21 +5453,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5481,10 +5481,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>586241</v>
+        <v>586434</v>
       </c>
       <c r="R46" t="n">
-        <v>7274946</v>
+        <v>7274786</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5553,10 +5553,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121533119</v>
+        <v>121532319</v>
       </c>
       <c r="B47" t="n">
-        <v>78609</v>
+        <v>90720</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5569,21 +5569,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5597,10 +5597,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>586262</v>
+        <v>586310</v>
       </c>
       <c r="R47" t="n">
-        <v>7274991</v>
+        <v>7274978</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5632,7 +5632,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5642,7 +5642,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5669,10 +5669,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121532535</v>
+        <v>121533188</v>
       </c>
       <c r="B48" t="n">
-        <v>79690</v>
+        <v>82393</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5685,21 +5685,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5713,10 +5713,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>586434</v>
+        <v>586262</v>
       </c>
       <c r="R48" t="n">
-        <v>7274786</v>
+        <v>7274991</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5748,7 +5748,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5785,10 +5785,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121533115</v>
+        <v>121532533</v>
       </c>
       <c r="B49" t="n">
-        <v>78609</v>
+        <v>79690</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5801,21 +5801,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5829,10 +5829,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>586409</v>
+        <v>586423</v>
       </c>
       <c r="R49" t="n">
-        <v>7274860</v>
+        <v>7274746</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5864,7 +5864,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5874,7 +5874,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5901,10 +5901,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121532446</v>
+        <v>121532632</v>
       </c>
       <c r="B50" t="n">
-        <v>79691</v>
+        <v>90716</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5917,21 +5917,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5945,10 +5945,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>586289</v>
+        <v>586372</v>
       </c>
       <c r="R50" t="n">
-        <v>7274978</v>
+        <v>7275002</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5980,7 +5980,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5990,7 +5990,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6017,10 +6017,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121532534</v>
+        <v>121532577</v>
       </c>
       <c r="B51" t="n">
-        <v>79690</v>
+        <v>78691</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6033,21 +6033,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>864</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -6061,10 +6061,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>586428</v>
+        <v>586262</v>
       </c>
       <c r="R51" t="n">
-        <v>7274781</v>
+        <v>7274991</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6096,7 +6096,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6106,7 +6106,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6133,10 +6133,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121533112</v>
+        <v>121532208</v>
       </c>
       <c r="B52" t="n">
-        <v>78609</v>
+        <v>91282</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6145,25 +6145,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>586773</v>
+        <v>586434</v>
       </c>
       <c r="R52" t="n">
-        <v>7274818</v>
+        <v>7274786</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6212,7 +6212,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6249,10 +6249,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121533188</v>
+        <v>121533119</v>
       </c>
       <c r="B53" t="n">
-        <v>82393</v>
+        <v>78609</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6265,21 +6265,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6338,7 +6338,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6365,10 +6365,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121532577</v>
+        <v>121532532</v>
       </c>
       <c r="B54" t="n">
-        <v>78691</v>
+        <v>79690</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6381,21 +6381,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>864</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -6409,10 +6409,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>586262</v>
+        <v>586670</v>
       </c>
       <c r="R54" t="n">
-        <v>7274991</v>
+        <v>7274637</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6481,10 +6481,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121532319</v>
+        <v>121532443</v>
       </c>
       <c r="B55" t="n">
-        <v>90720</v>
+        <v>79691</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6497,21 +6497,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -6525,10 +6525,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>586310</v>
+        <v>586360</v>
       </c>
       <c r="R55" t="n">
-        <v>7274978</v>
+        <v>7274887</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6560,7 +6560,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6570,7 +6570,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6597,7 +6597,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121532442</v>
+        <v>121532444</v>
       </c>
       <c r="B56" t="n">
         <v>79691</v>
@@ -6641,10 +6641,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>586409</v>
+        <v>586241</v>
       </c>
       <c r="R56" t="n">
-        <v>7274860</v>
+        <v>7274946</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6676,7 +6676,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6686,7 +6686,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6713,10 +6713,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121532632</v>
+        <v>121533115</v>
       </c>
       <c r="B57" t="n">
-        <v>90716</v>
+        <v>78609</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6729,21 +6729,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -6757,10 +6757,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>586372</v>
+        <v>586409</v>
       </c>
       <c r="R57" t="n">
-        <v>7275002</v>
+        <v>7274860</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6792,7 +6792,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6829,10 +6829,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121532533</v>
+        <v>121532630</v>
       </c>
       <c r="B58" t="n">
-        <v>79690</v>
+        <v>90716</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6845,21 +6845,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -6873,10 +6873,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>586423</v>
+        <v>586738</v>
       </c>
       <c r="R58" t="n">
-        <v>7274746</v>
+        <v>7274804</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6908,7 +6908,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6945,10 +6945,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121532630</v>
+        <v>121533112</v>
       </c>
       <c r="B59" t="n">
-        <v>90716</v>
+        <v>78609</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6961,21 +6961,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -6989,10 +6989,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>586738</v>
+        <v>586773</v>
       </c>
       <c r="R59" t="n">
-        <v>7274804</v>
+        <v>7274818</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7024,7 +7024,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7061,10 +7061,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121532208</v>
+        <v>121532534</v>
       </c>
       <c r="B60" t="n">
-        <v>91282</v>
+        <v>79690</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7073,25 +7073,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -7105,10 +7105,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>586434</v>
+        <v>586428</v>
       </c>
       <c r="R60" t="n">
-        <v>7274786</v>
+        <v>7274781</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7140,7 +7140,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7150,7 +7150,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD60" t="b">

--- a/artfynd/A 31945-2021 artfynd.xlsx
+++ b/artfynd/A 31945-2021 artfynd.xlsx
@@ -3063,10 +3063,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121476597</v>
+        <v>121476841</v>
       </c>
       <c r="B23" t="n">
-        <v>79691</v>
+        <v>90716</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3079,21 +3079,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3103,10 +3103,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>586361</v>
+        <v>586739</v>
       </c>
       <c r="R23" t="n">
-        <v>7274887</v>
+        <v>7274805</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3165,10 +3165,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121476441</v>
+        <v>121477385</v>
       </c>
       <c r="B24" t="n">
-        <v>90720</v>
+        <v>82393</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3181,21 +3181,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3205,10 +3205,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>586513</v>
+        <v>586263</v>
       </c>
       <c r="R24" t="n">
-        <v>7275037</v>
+        <v>7274991</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3267,10 +3267,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121477312</v>
+        <v>121476688</v>
       </c>
       <c r="B25" t="n">
-        <v>78609</v>
+        <v>91006</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3283,21 +3283,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3307,10 +3307,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>586774</v>
+        <v>586513</v>
       </c>
       <c r="R25" t="n">
-        <v>7274818</v>
+        <v>7275037</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3369,10 +3369,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121477315</v>
+        <v>121476521</v>
       </c>
       <c r="B26" t="n">
-        <v>78609</v>
+        <v>79556</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3385,21 +3385,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>388</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3409,10 +3409,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>586410</v>
+        <v>586320</v>
       </c>
       <c r="R26" t="n">
-        <v>7274861</v>
+        <v>7274981</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3471,10 +3471,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121476841</v>
+        <v>121476719</v>
       </c>
       <c r="B27" t="n">
-        <v>90716</v>
+        <v>79690</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3487,21 +3487,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>586739</v>
+        <v>586424</v>
       </c>
       <c r="R27" t="n">
-        <v>7274805</v>
+        <v>7274747</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3573,10 +3573,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121476721</v>
+        <v>121476790</v>
       </c>
       <c r="B28" t="n">
-        <v>79690</v>
+        <v>78691</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3589,21 +3589,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>864</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>586434</v>
+        <v>586263</v>
       </c>
       <c r="R28" t="n">
-        <v>7274787</v>
+        <v>7274991</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3675,10 +3675,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121476439</v>
+        <v>121476718</v>
       </c>
       <c r="B29" t="n">
-        <v>90720</v>
+        <v>79690</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3691,21 +3691,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3715,10 +3715,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>586310</v>
+        <v>586671</v>
       </c>
       <c r="R29" t="n">
-        <v>7274979</v>
+        <v>7274637</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3777,10 +3777,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121476718</v>
+        <v>121476843</v>
       </c>
       <c r="B30" t="n">
-        <v>79690</v>
+        <v>90716</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3793,21 +3793,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3817,10 +3817,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>586671</v>
+        <v>586373</v>
       </c>
       <c r="R30" t="n">
-        <v>7274637</v>
+        <v>7275002</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3879,10 +3879,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121476719</v>
+        <v>121476439</v>
       </c>
       <c r="B31" t="n">
-        <v>79690</v>
+        <v>90720</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3895,21 +3895,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3919,10 +3919,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>586424</v>
+        <v>586310</v>
       </c>
       <c r="R31" t="n">
-        <v>7274747</v>
+        <v>7274979</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3981,10 +3981,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121476688</v>
+        <v>121477312</v>
       </c>
       <c r="B32" t="n">
-        <v>91006</v>
+        <v>78609</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3997,21 +3997,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4021,10 +4021,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>586513</v>
+        <v>586774</v>
       </c>
       <c r="R32" t="n">
-        <v>7275037</v>
+        <v>7274818</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4083,10 +4083,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121477319</v>
+        <v>121476441</v>
       </c>
       <c r="B33" t="n">
-        <v>78609</v>
+        <v>90720</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4099,21 +4099,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4123,10 +4123,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>586263</v>
+        <v>586513</v>
       </c>
       <c r="R33" t="n">
-        <v>7274991</v>
+        <v>7275037</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4185,10 +4185,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121476595</v>
+        <v>121476846</v>
       </c>
       <c r="B34" t="n">
-        <v>79691</v>
+        <v>90716</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4201,21 +4201,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4225,10 +4225,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>586410</v>
+        <v>586623</v>
       </c>
       <c r="R34" t="n">
-        <v>7274861</v>
+        <v>7275057</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4287,10 +4287,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121476843</v>
+        <v>121476597</v>
       </c>
       <c r="B35" t="n">
-        <v>90716</v>
+        <v>79691</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4303,21 +4303,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4327,10 +4327,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>586373</v>
+        <v>586361</v>
       </c>
       <c r="R35" t="n">
-        <v>7275002</v>
+        <v>7274887</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4389,10 +4389,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121477385</v>
+        <v>121476600</v>
       </c>
       <c r="B36" t="n">
-        <v>82393</v>
+        <v>79691</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4405,21 +4405,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1312</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4429,10 +4429,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>586263</v>
+        <v>586290</v>
       </c>
       <c r="R36" t="n">
-        <v>7274991</v>
+        <v>7274978</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4491,10 +4491,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121476598</v>
+        <v>121477395</v>
       </c>
       <c r="B37" t="n">
-        <v>79691</v>
+        <v>88039</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4507,21 +4507,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2081</v>
+        <v>510</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4531,10 +4531,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>586242</v>
+        <v>586434</v>
       </c>
       <c r="R37" t="n">
-        <v>7274946</v>
+        <v>7274787</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4593,10 +4593,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121476600</v>
+        <v>121476721</v>
       </c>
       <c r="B38" t="n">
-        <v>79691</v>
+        <v>79690</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4609,21 +4609,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4633,10 +4633,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>586290</v>
+        <v>586434</v>
       </c>
       <c r="R38" t="n">
-        <v>7274978</v>
+        <v>7274787</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4695,10 +4695,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121476846</v>
+        <v>121476595</v>
       </c>
       <c r="B39" t="n">
-        <v>90716</v>
+        <v>79691</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4711,21 +4711,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>586623</v>
+        <v>586410</v>
       </c>
       <c r="R39" t="n">
-        <v>7275057</v>
+        <v>7274861</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4797,10 +4797,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121477395</v>
+        <v>121477315</v>
       </c>
       <c r="B40" t="n">
-        <v>88039</v>
+        <v>78609</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4813,21 +4813,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4837,10 +4837,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>586434</v>
+        <v>586410</v>
       </c>
       <c r="R40" t="n">
-        <v>7274787</v>
+        <v>7274861</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4899,10 +4899,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121476720</v>
+        <v>121477319</v>
       </c>
       <c r="B41" t="n">
-        <v>79690</v>
+        <v>78609</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4915,21 +4915,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4939,10 +4939,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>586428</v>
+        <v>586263</v>
       </c>
       <c r="R41" t="n">
-        <v>7274782</v>
+        <v>7274991</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5001,10 +5001,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121476521</v>
+        <v>121476720</v>
       </c>
       <c r="B42" t="n">
-        <v>79556</v>
+        <v>79690</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5017,21 +5017,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>388</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5041,10 +5041,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>586320</v>
+        <v>586428</v>
       </c>
       <c r="R42" t="n">
-        <v>7274981</v>
+        <v>7274782</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5103,10 +5103,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121476790</v>
+        <v>121476598</v>
       </c>
       <c r="B43" t="n">
-        <v>78691</v>
+        <v>79691</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5119,21 +5119,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5143,10 +5143,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>586263</v>
+        <v>586242</v>
       </c>
       <c r="R43" t="n">
-        <v>7274991</v>
+        <v>7274946</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5205,10 +5205,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121532446</v>
+        <v>121532632</v>
       </c>
       <c r="B44" t="n">
-        <v>79691</v>
+        <v>90716</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5221,21 +5221,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5249,10 +5249,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>586289</v>
+        <v>586372</v>
       </c>
       <c r="R44" t="n">
-        <v>7274978</v>
+        <v>7275002</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5321,10 +5321,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121532442</v>
+        <v>121533119</v>
       </c>
       <c r="B45" t="n">
-        <v>79691</v>
+        <v>78609</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5337,21 +5337,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5365,10 +5365,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>586409</v>
+        <v>586262</v>
       </c>
       <c r="R45" t="n">
-        <v>7274860</v>
+        <v>7274991</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5400,7 +5400,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5410,7 +5410,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5437,10 +5437,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121532535</v>
+        <v>121532444</v>
       </c>
       <c r="B46" t="n">
-        <v>79690</v>
+        <v>79691</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5453,21 +5453,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5481,10 +5481,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>586434</v>
+        <v>586241</v>
       </c>
       <c r="R46" t="n">
-        <v>7274786</v>
+        <v>7274946</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5553,10 +5553,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121532319</v>
+        <v>121533188</v>
       </c>
       <c r="B47" t="n">
-        <v>90720</v>
+        <v>82393</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5569,21 +5569,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5597,10 +5597,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>586310</v>
+        <v>586262</v>
       </c>
       <c r="R47" t="n">
-        <v>7274978</v>
+        <v>7274991</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5632,7 +5632,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5642,7 +5642,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5669,10 +5669,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121533188</v>
+        <v>121532533</v>
       </c>
       <c r="B48" t="n">
-        <v>82393</v>
+        <v>79690</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5685,21 +5685,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5713,10 +5713,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>586262</v>
+        <v>586423</v>
       </c>
       <c r="R48" t="n">
-        <v>7274991</v>
+        <v>7274746</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5748,7 +5748,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5785,10 +5785,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121532533</v>
+        <v>121532208</v>
       </c>
       <c r="B49" t="n">
-        <v>79690</v>
+        <v>91282</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5797,25 +5797,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5829,10 +5829,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>586423</v>
+        <v>586434</v>
       </c>
       <c r="R49" t="n">
-        <v>7274746</v>
+        <v>7274786</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5864,7 +5864,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5874,7 +5874,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5901,10 +5901,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121532632</v>
+        <v>121532446</v>
       </c>
       <c r="B50" t="n">
-        <v>90716</v>
+        <v>79691</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5917,21 +5917,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5945,10 +5945,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>586372</v>
+        <v>586289</v>
       </c>
       <c r="R50" t="n">
-        <v>7275002</v>
+        <v>7274978</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5980,7 +5980,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5990,7 +5990,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6133,10 +6133,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121532208</v>
+        <v>121532442</v>
       </c>
       <c r="B52" t="n">
-        <v>91282</v>
+        <v>79691</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6145,25 +6145,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>760</v>
+        <v>2081</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>586434</v>
+        <v>586409</v>
       </c>
       <c r="R52" t="n">
-        <v>7274786</v>
+        <v>7274860</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6212,7 +6212,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6249,7 +6249,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121533119</v>
+        <v>121533115</v>
       </c>
       <c r="B53" t="n">
         <v>78609</v>
@@ -6293,10 +6293,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>586262</v>
+        <v>586409</v>
       </c>
       <c r="R53" t="n">
-        <v>7274991</v>
+        <v>7274860</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6328,7 +6328,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6338,7 +6338,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6365,7 +6365,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121532532</v>
+        <v>121532535</v>
       </c>
       <c r="B54" t="n">
         <v>79690</v>
@@ -6409,10 +6409,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>586670</v>
+        <v>586434</v>
       </c>
       <c r="R54" t="n">
-        <v>7274637</v>
+        <v>7274786</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6481,10 +6481,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121532443</v>
+        <v>121532532</v>
       </c>
       <c r="B55" t="n">
-        <v>79691</v>
+        <v>79690</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6497,21 +6497,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -6525,10 +6525,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>586360</v>
+        <v>586670</v>
       </c>
       <c r="R55" t="n">
-        <v>7274887</v>
+        <v>7274637</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6560,7 +6560,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6570,7 +6570,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6597,10 +6597,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121532444</v>
+        <v>121532630</v>
       </c>
       <c r="B56" t="n">
-        <v>79691</v>
+        <v>90716</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6613,21 +6613,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -6641,10 +6641,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>586241</v>
+        <v>586738</v>
       </c>
       <c r="R56" t="n">
-        <v>7274946</v>
+        <v>7274804</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6676,7 +6676,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6686,7 +6686,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6713,7 +6713,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121533115</v>
+        <v>121533112</v>
       </c>
       <c r="B57" t="n">
         <v>78609</v>
@@ -6757,10 +6757,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>586409</v>
+        <v>586773</v>
       </c>
       <c r="R57" t="n">
-        <v>7274860</v>
+        <v>7274818</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6792,7 +6792,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6829,10 +6829,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121532630</v>
+        <v>121532319</v>
       </c>
       <c r="B58" t="n">
-        <v>90716</v>
+        <v>90720</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6845,21 +6845,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -6873,10 +6873,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>586738</v>
+        <v>586310</v>
       </c>
       <c r="R58" t="n">
-        <v>7274804</v>
+        <v>7274978</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6908,7 +6908,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6945,10 +6945,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121533112</v>
+        <v>121532443</v>
       </c>
       <c r="B59" t="n">
-        <v>78609</v>
+        <v>79691</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6961,21 +6961,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -6989,10 +6989,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>586773</v>
+        <v>586360</v>
       </c>
       <c r="R59" t="n">
-        <v>7274818</v>
+        <v>7274887</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7024,7 +7024,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD59" t="b">

--- a/artfynd/A 31945-2021 artfynd.xlsx
+++ b/artfynd/A 31945-2021 artfynd.xlsx
@@ -3471,10 +3471,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121476719</v>
+        <v>121476790</v>
       </c>
       <c r="B27" t="n">
-        <v>79690</v>
+        <v>78691</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3487,21 +3487,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>864</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>586424</v>
+        <v>586263</v>
       </c>
       <c r="R27" t="n">
-        <v>7274747</v>
+        <v>7274991</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3573,10 +3573,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121476790</v>
+        <v>121476719</v>
       </c>
       <c r="B28" t="n">
-        <v>78691</v>
+        <v>79690</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3589,21 +3589,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>864</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>586263</v>
+        <v>586424</v>
       </c>
       <c r="R28" t="n">
-        <v>7274991</v>
+        <v>7274747</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -6017,10 +6017,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121532577</v>
+        <v>121532442</v>
       </c>
       <c r="B51" t="n">
-        <v>78691</v>
+        <v>79691</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6033,21 +6033,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -6061,10 +6061,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>586262</v>
+        <v>586409</v>
       </c>
       <c r="R51" t="n">
-        <v>7274991</v>
+        <v>7274860</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6096,7 +6096,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6106,7 +6106,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6133,10 +6133,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121532442</v>
+        <v>121532577</v>
       </c>
       <c r="B52" t="n">
-        <v>79691</v>
+        <v>78691</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6149,21 +6149,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>586409</v>
+        <v>586262</v>
       </c>
       <c r="R52" t="n">
-        <v>7274860</v>
+        <v>7274991</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6212,7 +6212,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 31945-2021 artfynd.xlsx
+++ b/artfynd/A 31945-2021 artfynd.xlsx
@@ -3471,10 +3471,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121476790</v>
+        <v>121476719</v>
       </c>
       <c r="B27" t="n">
-        <v>78691</v>
+        <v>79690</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3487,21 +3487,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>864</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>586263</v>
+        <v>586424</v>
       </c>
       <c r="R27" t="n">
-        <v>7274991</v>
+        <v>7274747</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3573,10 +3573,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121476719</v>
+        <v>121476790</v>
       </c>
       <c r="B28" t="n">
-        <v>79690</v>
+        <v>78691</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3589,21 +3589,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>864</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>586424</v>
+        <v>586263</v>
       </c>
       <c r="R28" t="n">
-        <v>7274747</v>
+        <v>7274991</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -6017,10 +6017,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121532442</v>
+        <v>121532577</v>
       </c>
       <c r="B51" t="n">
-        <v>79691</v>
+        <v>78691</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6033,21 +6033,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -6061,10 +6061,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>586409</v>
+        <v>586262</v>
       </c>
       <c r="R51" t="n">
-        <v>7274860</v>
+        <v>7274991</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6096,7 +6096,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6106,7 +6106,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6133,10 +6133,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121532577</v>
+        <v>121532442</v>
       </c>
       <c r="B52" t="n">
-        <v>78691</v>
+        <v>79691</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6149,21 +6149,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>586262</v>
+        <v>586409</v>
       </c>
       <c r="R52" t="n">
-        <v>7274991</v>
+        <v>7274860</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6212,7 +6212,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6365,10 +6365,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121532535</v>
+        <v>121532630</v>
       </c>
       <c r="B54" t="n">
-        <v>79690</v>
+        <v>90716</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6381,21 +6381,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -6409,10 +6409,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>586434</v>
+        <v>586738</v>
       </c>
       <c r="R54" t="n">
-        <v>7274786</v>
+        <v>7274804</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6481,7 +6481,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121532532</v>
+        <v>121532535</v>
       </c>
       <c r="B55" t="n">
         <v>79690</v>
@@ -6525,10 +6525,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>586670</v>
+        <v>586434</v>
       </c>
       <c r="R55" t="n">
-        <v>7274637</v>
+        <v>7274786</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6560,7 +6560,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6570,7 +6570,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6597,10 +6597,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121532630</v>
+        <v>121532532</v>
       </c>
       <c r="B56" t="n">
-        <v>90716</v>
+        <v>79690</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6613,21 +6613,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -6641,10 +6641,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>586738</v>
+        <v>586670</v>
       </c>
       <c r="R56" t="n">
-        <v>7274804</v>
+        <v>7274637</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6676,7 +6676,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6686,7 +6686,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AD56" t="b">

--- a/artfynd/A 31945-2021 artfynd.xlsx
+++ b/artfynd/A 31945-2021 artfynd.xlsx
@@ -3063,10 +3063,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121476841</v>
+        <v>121476843</v>
       </c>
       <c r="B23" t="n">
-        <v>90716</v>
+        <v>90724</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3103,10 +3103,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>586739</v>
+        <v>586373</v>
       </c>
       <c r="R23" t="n">
-        <v>7274805</v>
+        <v>7275002</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3165,10 +3165,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121477385</v>
+        <v>121476595</v>
       </c>
       <c r="B24" t="n">
-        <v>82393</v>
+        <v>79698</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3181,21 +3181,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3205,10 +3205,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>586263</v>
+        <v>586410</v>
       </c>
       <c r="R24" t="n">
-        <v>7274991</v>
+        <v>7274861</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3267,10 +3267,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121476688</v>
+        <v>121476598</v>
       </c>
       <c r="B25" t="n">
-        <v>91006</v>
+        <v>79698</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3283,21 +3283,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3307,10 +3307,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>586513</v>
+        <v>586242</v>
       </c>
       <c r="R25" t="n">
-        <v>7275037</v>
+        <v>7274946</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3369,10 +3369,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121476521</v>
+        <v>121476718</v>
       </c>
       <c r="B26" t="n">
-        <v>79556</v>
+        <v>79697</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3385,21 +3385,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>388</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3409,10 +3409,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>586320</v>
+        <v>586671</v>
       </c>
       <c r="R26" t="n">
-        <v>7274981</v>
+        <v>7274637</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3471,10 +3471,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121476719</v>
+        <v>121477315</v>
       </c>
       <c r="B27" t="n">
-        <v>79690</v>
+        <v>78616</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3487,21 +3487,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>586424</v>
+        <v>586410</v>
       </c>
       <c r="R27" t="n">
-        <v>7274747</v>
+        <v>7274861</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3576,7 +3576,7 @@
         <v>121476790</v>
       </c>
       <c r="B28" t="n">
-        <v>78691</v>
+        <v>78698</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3675,10 +3675,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121476718</v>
+        <v>121476719</v>
       </c>
       <c r="B29" t="n">
-        <v>79690</v>
+        <v>79697</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3715,10 +3715,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>586671</v>
+        <v>586424</v>
       </c>
       <c r="R29" t="n">
-        <v>7274637</v>
+        <v>7274747</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3777,10 +3777,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121476843</v>
+        <v>121477395</v>
       </c>
       <c r="B30" t="n">
-        <v>90716</v>
+        <v>88046</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3793,21 +3793,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1108</v>
+        <v>510</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3817,10 +3817,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>586373</v>
+        <v>586434</v>
       </c>
       <c r="R30" t="n">
-        <v>7275002</v>
+        <v>7274787</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3879,10 +3879,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121476439</v>
+        <v>121476600</v>
       </c>
       <c r="B31" t="n">
-        <v>90720</v>
+        <v>79698</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3895,21 +3895,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3919,10 +3919,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>586310</v>
+        <v>586290</v>
       </c>
       <c r="R31" t="n">
-        <v>7274979</v>
+        <v>7274978</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3981,10 +3981,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121477312</v>
+        <v>121476721</v>
       </c>
       <c r="B32" t="n">
-        <v>78609</v>
+        <v>79697</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3997,21 +3997,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4021,10 +4021,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>586774</v>
+        <v>586434</v>
       </c>
       <c r="R32" t="n">
-        <v>7274818</v>
+        <v>7274787</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4083,10 +4083,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121476441</v>
+        <v>121477319</v>
       </c>
       <c r="B33" t="n">
-        <v>90720</v>
+        <v>78616</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4099,21 +4099,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4123,10 +4123,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>586513</v>
+        <v>586263</v>
       </c>
       <c r="R33" t="n">
-        <v>7275037</v>
+        <v>7274991</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4185,10 +4185,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121476846</v>
+        <v>121476720</v>
       </c>
       <c r="B34" t="n">
-        <v>90716</v>
+        <v>79697</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4201,21 +4201,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4225,10 +4225,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>586623</v>
+        <v>586428</v>
       </c>
       <c r="R34" t="n">
-        <v>7275057</v>
+        <v>7274782</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4287,10 +4287,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121476597</v>
+        <v>121476841</v>
       </c>
       <c r="B35" t="n">
-        <v>79691</v>
+        <v>90724</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4303,21 +4303,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4327,10 +4327,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>586361</v>
+        <v>586739</v>
       </c>
       <c r="R35" t="n">
-        <v>7274887</v>
+        <v>7274805</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4389,10 +4389,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121476600</v>
+        <v>121476521</v>
       </c>
       <c r="B36" t="n">
-        <v>79691</v>
+        <v>79563</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4405,21 +4405,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2081</v>
+        <v>388</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4429,10 +4429,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>586290</v>
+        <v>586320</v>
       </c>
       <c r="R36" t="n">
-        <v>7274978</v>
+        <v>7274981</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4491,10 +4491,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121477395</v>
+        <v>121476688</v>
       </c>
       <c r="B37" t="n">
-        <v>88039</v>
+        <v>91014</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4507,21 +4507,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>510</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4531,10 +4531,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>586434</v>
+        <v>586513</v>
       </c>
       <c r="R37" t="n">
-        <v>7274787</v>
+        <v>7275037</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4593,10 +4593,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121476721</v>
+        <v>121476597</v>
       </c>
       <c r="B38" t="n">
-        <v>79690</v>
+        <v>79698</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4609,21 +4609,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4633,10 +4633,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>586434</v>
+        <v>586361</v>
       </c>
       <c r="R38" t="n">
-        <v>7274787</v>
+        <v>7274887</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4695,10 +4695,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121476595</v>
+        <v>121477312</v>
       </c>
       <c r="B39" t="n">
-        <v>79691</v>
+        <v>78616</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4711,21 +4711,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>586410</v>
+        <v>586774</v>
       </c>
       <c r="R39" t="n">
-        <v>7274861</v>
+        <v>7274818</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4797,10 +4797,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121477315</v>
+        <v>121476441</v>
       </c>
       <c r="B40" t="n">
-        <v>78609</v>
+        <v>90728</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4813,21 +4813,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4837,10 +4837,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>586410</v>
+        <v>586513</v>
       </c>
       <c r="R40" t="n">
-        <v>7274861</v>
+        <v>7275037</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4899,10 +4899,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121477319</v>
+        <v>121477385</v>
       </c>
       <c r="B41" t="n">
-        <v>78609</v>
+        <v>82400</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4915,21 +4915,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5001,10 +5001,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121476720</v>
+        <v>121476846</v>
       </c>
       <c r="B42" t="n">
-        <v>79690</v>
+        <v>90724</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5017,21 +5017,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5041,10 +5041,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>586428</v>
+        <v>586623</v>
       </c>
       <c r="R42" t="n">
-        <v>7274782</v>
+        <v>7275057</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5103,10 +5103,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121476598</v>
+        <v>121476439</v>
       </c>
       <c r="B43" t="n">
-        <v>79691</v>
+        <v>90728</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5119,21 +5119,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5143,10 +5143,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>586242</v>
+        <v>586310</v>
       </c>
       <c r="R43" t="n">
-        <v>7274946</v>
+        <v>7274979</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5205,10 +5205,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121532632</v>
+        <v>121532319</v>
       </c>
       <c r="B44" t="n">
-        <v>90716</v>
+        <v>90728</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5221,21 +5221,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5249,10 +5249,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>586372</v>
+        <v>586310</v>
       </c>
       <c r="R44" t="n">
-        <v>7275002</v>
+        <v>7274978</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5321,10 +5321,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121533119</v>
+        <v>121532534</v>
       </c>
       <c r="B45" t="n">
-        <v>78609</v>
+        <v>79697</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5337,21 +5337,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5365,10 +5365,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>586262</v>
+        <v>586428</v>
       </c>
       <c r="R45" t="n">
-        <v>7274991</v>
+        <v>7274781</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5400,7 +5400,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5410,7 +5410,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5437,10 +5437,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121532444</v>
+        <v>121532442</v>
       </c>
       <c r="B46" t="n">
-        <v>79691</v>
+        <v>79698</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5481,10 +5481,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>586241</v>
+        <v>586409</v>
       </c>
       <c r="R46" t="n">
-        <v>7274946</v>
+        <v>7274860</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5553,10 +5553,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121533188</v>
+        <v>121532208</v>
       </c>
       <c r="B47" t="n">
-        <v>82393</v>
+        <v>91290</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5565,25 +5565,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1312</v>
+        <v>760</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5597,10 +5597,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>586262</v>
+        <v>586434</v>
       </c>
       <c r="R47" t="n">
-        <v>7274991</v>
+        <v>7274786</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5632,7 +5632,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5642,7 +5642,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5669,10 +5669,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121532533</v>
+        <v>121532446</v>
       </c>
       <c r="B48" t="n">
-        <v>79690</v>
+        <v>79698</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5685,21 +5685,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5713,10 +5713,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>586423</v>
+        <v>586289</v>
       </c>
       <c r="R48" t="n">
-        <v>7274746</v>
+        <v>7274978</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5748,7 +5748,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5785,10 +5785,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121532208</v>
+        <v>121532535</v>
       </c>
       <c r="B49" t="n">
-        <v>91282</v>
+        <v>79697</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5797,25 +5797,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5864,7 +5864,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5874,7 +5874,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5901,10 +5901,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121532446</v>
+        <v>121532532</v>
       </c>
       <c r="B50" t="n">
-        <v>79691</v>
+        <v>79697</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5917,21 +5917,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5945,10 +5945,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>586289</v>
+        <v>586670</v>
       </c>
       <c r="R50" t="n">
-        <v>7274978</v>
+        <v>7274637</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5980,7 +5980,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5990,7 +5990,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6017,10 +6017,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121532577</v>
+        <v>121532533</v>
       </c>
       <c r="B51" t="n">
-        <v>78691</v>
+        <v>79697</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6033,21 +6033,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>864</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -6061,10 +6061,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>586262</v>
+        <v>586423</v>
       </c>
       <c r="R51" t="n">
-        <v>7274991</v>
+        <v>7274746</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6096,7 +6096,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6106,7 +6106,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6133,10 +6133,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121532442</v>
+        <v>121533112</v>
       </c>
       <c r="B52" t="n">
-        <v>79691</v>
+        <v>78616</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6149,21 +6149,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>586409</v>
+        <v>586773</v>
       </c>
       <c r="R52" t="n">
-        <v>7274860</v>
+        <v>7274818</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6212,7 +6212,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6252,7 +6252,7 @@
         <v>121533115</v>
       </c>
       <c r="B53" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6365,10 +6365,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121532630</v>
+        <v>121533119</v>
       </c>
       <c r="B54" t="n">
-        <v>90716</v>
+        <v>78616</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6381,21 +6381,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -6409,10 +6409,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>586738</v>
+        <v>586262</v>
       </c>
       <c r="R54" t="n">
-        <v>7274804</v>
+        <v>7274991</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6481,10 +6481,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121532535</v>
+        <v>121532577</v>
       </c>
       <c r="B55" t="n">
-        <v>79690</v>
+        <v>78698</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6497,21 +6497,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>864</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -6525,10 +6525,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>586434</v>
+        <v>586262</v>
       </c>
       <c r="R55" t="n">
-        <v>7274786</v>
+        <v>7274991</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6560,7 +6560,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6570,7 +6570,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6597,10 +6597,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121532532</v>
+        <v>121533188</v>
       </c>
       <c r="B56" t="n">
-        <v>79690</v>
+        <v>82400</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6613,21 +6613,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -6641,10 +6641,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>586670</v>
+        <v>586262</v>
       </c>
       <c r="R56" t="n">
-        <v>7274637</v>
+        <v>7274991</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6676,7 +6676,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6686,7 +6686,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6713,10 +6713,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121533112</v>
+        <v>121532630</v>
       </c>
       <c r="B57" t="n">
-        <v>78609</v>
+        <v>90724</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6729,21 +6729,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -6757,10 +6757,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>586773</v>
+        <v>586738</v>
       </c>
       <c r="R57" t="n">
-        <v>7274818</v>
+        <v>7274804</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6792,7 +6792,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6829,10 +6829,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121532319</v>
+        <v>121532632</v>
       </c>
       <c r="B58" t="n">
-        <v>90720</v>
+        <v>90724</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6845,21 +6845,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -6873,10 +6873,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>586310</v>
+        <v>586372</v>
       </c>
       <c r="R58" t="n">
-        <v>7274978</v>
+        <v>7275002</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6908,7 +6908,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6948,7 +6948,7 @@
         <v>121532443</v>
       </c>
       <c r="B59" t="n">
-        <v>79691</v>
+        <v>79698</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7061,10 +7061,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121532534</v>
+        <v>121532444</v>
       </c>
       <c r="B60" t="n">
-        <v>79690</v>
+        <v>79698</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7077,21 +7077,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -7105,10 +7105,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>586428</v>
+        <v>586241</v>
       </c>
       <c r="R60" t="n">
-        <v>7274781</v>
+        <v>7274946</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7140,7 +7140,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7150,7 +7150,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD60" t="b">

--- a/artfynd/A 31945-2021 artfynd.xlsx
+++ b/artfynd/A 31945-2021 artfynd.xlsx
@@ -4695,10 +4695,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121477312</v>
+        <v>121476441</v>
       </c>
       <c r="B39" t="n">
-        <v>78616</v>
+        <v>90728</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4711,21 +4711,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>586774</v>
+        <v>586513</v>
       </c>
       <c r="R39" t="n">
-        <v>7274818</v>
+        <v>7275037</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4797,10 +4797,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121476441</v>
+        <v>121477385</v>
       </c>
       <c r="B40" t="n">
-        <v>90728</v>
+        <v>82400</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4813,21 +4813,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4837,10 +4837,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>586513</v>
+        <v>586263</v>
       </c>
       <c r="R40" t="n">
-        <v>7275037</v>
+        <v>7274991</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4899,10 +4899,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121477385</v>
+        <v>121477312</v>
       </c>
       <c r="B41" t="n">
-        <v>82400</v>
+        <v>78616</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4915,21 +4915,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4939,10 +4939,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>586263</v>
+        <v>586774</v>
       </c>
       <c r="R41" t="n">
-        <v>7274991</v>
+        <v>7274818</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>

--- a/artfynd/A 31945-2021 artfynd.xlsx
+++ b/artfynd/A 31945-2021 artfynd.xlsx
@@ -6481,10 +6481,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121532577</v>
+        <v>121533188</v>
       </c>
       <c r="B55" t="n">
-        <v>78698</v>
+        <v>82400</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6497,21 +6497,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>864</v>
+        <v>1312</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -6560,7 +6560,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6570,7 +6570,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6597,10 +6597,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121533188</v>
+        <v>121532577</v>
       </c>
       <c r="B56" t="n">
-        <v>82400</v>
+        <v>78698</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6613,21 +6613,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -6676,7 +6676,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6686,7 +6686,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="AD56" t="b">

--- a/artfynd/A 31945-2021 artfynd.xlsx
+++ b/artfynd/A 31945-2021 artfynd.xlsx
@@ -3063,10 +3063,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121476846</v>
+        <v>121477315</v>
       </c>
       <c r="B23" t="n">
-        <v>90724</v>
+        <v>78616</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3079,21 +3079,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3103,10 +3103,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>586623</v>
+        <v>586410</v>
       </c>
       <c r="R23" t="n">
-        <v>7275057</v>
+        <v>7274861</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3267,10 +3267,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121477312</v>
+        <v>121476720</v>
       </c>
       <c r="B25" t="n">
-        <v>78616</v>
+        <v>79697</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3283,21 +3283,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3307,10 +3307,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>586774</v>
+        <v>586428</v>
       </c>
       <c r="R25" t="n">
-        <v>7274818</v>
+        <v>7274782</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3369,10 +3369,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121476441</v>
+        <v>121477312</v>
       </c>
       <c r="B26" t="n">
-        <v>90728</v>
+        <v>78616</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3385,21 +3385,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3409,10 +3409,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>586513</v>
+        <v>586774</v>
       </c>
       <c r="R26" t="n">
-        <v>7275037</v>
+        <v>7274818</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3471,10 +3471,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121476790</v>
+        <v>121476521</v>
       </c>
       <c r="B27" t="n">
-        <v>78698</v>
+        <v>79563</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3487,21 +3487,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>864</v>
+        <v>388</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>586263</v>
+        <v>586320</v>
       </c>
       <c r="R27" t="n">
-        <v>7274991</v>
+        <v>7274981</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3675,10 +3675,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121477315</v>
+        <v>121476688</v>
       </c>
       <c r="B29" t="n">
-        <v>78616</v>
+        <v>91014</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3691,21 +3691,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3715,10 +3715,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>586410</v>
+        <v>586513</v>
       </c>
       <c r="R29" t="n">
-        <v>7274861</v>
+        <v>7275037</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3777,10 +3777,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121476721</v>
+        <v>121477319</v>
       </c>
       <c r="B30" t="n">
-        <v>79697</v>
+        <v>78616</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3793,21 +3793,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3817,10 +3817,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>586434</v>
+        <v>586263</v>
       </c>
       <c r="R30" t="n">
-        <v>7274787</v>
+        <v>7274991</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3879,10 +3879,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121476688</v>
+        <v>121476841</v>
       </c>
       <c r="B31" t="n">
-        <v>91014</v>
+        <v>90724</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3895,21 +3895,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3919,10 +3919,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>586513</v>
+        <v>586739</v>
       </c>
       <c r="R31" t="n">
-        <v>7275037</v>
+        <v>7274805</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3981,10 +3981,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121476841</v>
+        <v>121476600</v>
       </c>
       <c r="B32" t="n">
-        <v>90724</v>
+        <v>79698</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3997,21 +3997,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4021,10 +4021,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>586739</v>
+        <v>586290</v>
       </c>
       <c r="R32" t="n">
-        <v>7274805</v>
+        <v>7274978</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4083,10 +4083,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121476597</v>
+        <v>121477385</v>
       </c>
       <c r="B33" t="n">
-        <v>79698</v>
+        <v>82400</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4099,21 +4099,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4123,10 +4123,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>586361</v>
+        <v>586263</v>
       </c>
       <c r="R33" t="n">
-        <v>7274887</v>
+        <v>7274991</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4185,10 +4185,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121476600</v>
+        <v>121476843</v>
       </c>
       <c r="B34" t="n">
-        <v>79698</v>
+        <v>90724</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4201,21 +4201,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4225,10 +4225,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>586290</v>
+        <v>586373</v>
       </c>
       <c r="R34" t="n">
-        <v>7274978</v>
+        <v>7275002</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4287,10 +4287,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121476719</v>
+        <v>121476441</v>
       </c>
       <c r="B35" t="n">
-        <v>79697</v>
+        <v>90728</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4303,21 +4303,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4327,10 +4327,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>586424</v>
+        <v>586513</v>
       </c>
       <c r="R35" t="n">
-        <v>7274747</v>
+        <v>7275037</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4389,7 +4389,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121476720</v>
+        <v>121476721</v>
       </c>
       <c r="B36" t="n">
         <v>79697</v>
@@ -4429,10 +4429,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>586428</v>
+        <v>586434</v>
       </c>
       <c r="R36" t="n">
-        <v>7274782</v>
+        <v>7274787</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4491,10 +4491,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121477319</v>
+        <v>121476846</v>
       </c>
       <c r="B37" t="n">
-        <v>78616</v>
+        <v>90724</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4507,21 +4507,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4531,10 +4531,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>586263</v>
+        <v>586623</v>
       </c>
       <c r="R37" t="n">
-        <v>7274991</v>
+        <v>7275057</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4593,10 +4593,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121476718</v>
+        <v>121477395</v>
       </c>
       <c r="B38" t="n">
-        <v>79697</v>
+        <v>88046</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4609,21 +4609,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4633,10 +4633,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>586671</v>
+        <v>586434</v>
       </c>
       <c r="R38" t="n">
-        <v>7274637</v>
+        <v>7274787</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4797,10 +4797,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121477385</v>
+        <v>121476719</v>
       </c>
       <c r="B40" t="n">
-        <v>82400</v>
+        <v>79697</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4813,21 +4813,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4837,10 +4837,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>586263</v>
+        <v>586424</v>
       </c>
       <c r="R40" t="n">
-        <v>7274991</v>
+        <v>7274747</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4899,10 +4899,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121476521</v>
+        <v>121476718</v>
       </c>
       <c r="B41" t="n">
-        <v>79563</v>
+        <v>79697</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4915,21 +4915,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>388</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4939,10 +4939,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>586320</v>
+        <v>586671</v>
       </c>
       <c r="R41" t="n">
-        <v>7274981</v>
+        <v>7274637</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5001,10 +5001,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121477395</v>
+        <v>121476790</v>
       </c>
       <c r="B42" t="n">
-        <v>88046</v>
+        <v>78698</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5017,21 +5017,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>510</v>
+        <v>864</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5041,10 +5041,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>586434</v>
+        <v>586263</v>
       </c>
       <c r="R42" t="n">
-        <v>7274787</v>
+        <v>7274991</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5103,10 +5103,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121476843</v>
+        <v>121476597</v>
       </c>
       <c r="B43" t="n">
-        <v>90724</v>
+        <v>79698</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5119,21 +5119,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5143,10 +5143,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>586373</v>
+        <v>586361</v>
       </c>
       <c r="R43" t="n">
-        <v>7275002</v>
+        <v>7274887</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5205,10 +5205,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121533188</v>
+        <v>121533112</v>
       </c>
       <c r="B44" t="n">
-        <v>82400</v>
+        <v>78616</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5221,21 +5221,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5249,10 +5249,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>586262</v>
+        <v>586773</v>
       </c>
       <c r="R44" t="n">
-        <v>7274991</v>
+        <v>7274818</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5437,10 +5437,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121532577</v>
+        <v>121533115</v>
       </c>
       <c r="B46" t="n">
-        <v>78698</v>
+        <v>78616</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5453,21 +5453,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5481,10 +5481,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>586262</v>
+        <v>586409</v>
       </c>
       <c r="R46" t="n">
-        <v>7274991</v>
+        <v>7274860</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5553,10 +5553,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121532533</v>
+        <v>121532577</v>
       </c>
       <c r="B47" t="n">
-        <v>79697</v>
+        <v>78698</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5569,21 +5569,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>864</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5597,10 +5597,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>586423</v>
+        <v>586262</v>
       </c>
       <c r="R47" t="n">
-        <v>7274746</v>
+        <v>7274991</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5632,7 +5632,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5642,7 +5642,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5669,10 +5669,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121533112</v>
+        <v>121532632</v>
       </c>
       <c r="B48" t="n">
-        <v>78616</v>
+        <v>90724</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5685,21 +5685,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5713,10 +5713,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>586773</v>
+        <v>586372</v>
       </c>
       <c r="R48" t="n">
-        <v>7274818</v>
+        <v>7275002</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5748,7 +5748,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5785,10 +5785,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121532208</v>
+        <v>121532443</v>
       </c>
       <c r="B49" t="n">
-        <v>91290</v>
+        <v>79698</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5797,25 +5797,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>760</v>
+        <v>2081</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5829,10 +5829,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>586434</v>
+        <v>586360</v>
       </c>
       <c r="R49" t="n">
-        <v>7274786</v>
+        <v>7274887</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5864,7 +5864,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5874,7 +5874,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5901,10 +5901,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121533119</v>
+        <v>121532532</v>
       </c>
       <c r="B50" t="n">
-        <v>78616</v>
+        <v>79697</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5917,21 +5917,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5945,10 +5945,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>586262</v>
+        <v>586670</v>
       </c>
       <c r="R50" t="n">
-        <v>7274991</v>
+        <v>7274637</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5980,7 +5980,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5990,7 +5990,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6017,10 +6017,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121532534</v>
+        <v>121532446</v>
       </c>
       <c r="B51" t="n">
-        <v>79697</v>
+        <v>79698</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6033,21 +6033,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -6061,10 +6061,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>586428</v>
+        <v>586289</v>
       </c>
       <c r="R51" t="n">
-        <v>7274781</v>
+        <v>7274978</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6096,7 +6096,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6106,7 +6106,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6249,10 +6249,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121532632</v>
+        <v>121532208</v>
       </c>
       <c r="B53" t="n">
-        <v>90724</v>
+        <v>91290</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6261,25 +6261,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1108</v>
+        <v>760</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -6293,10 +6293,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>586372</v>
+        <v>586434</v>
       </c>
       <c r="R53" t="n">
-        <v>7275002</v>
+        <v>7274786</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6328,7 +6328,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6338,7 +6338,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6365,10 +6365,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121532443</v>
+        <v>121532630</v>
       </c>
       <c r="B54" t="n">
-        <v>79698</v>
+        <v>90724</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6381,21 +6381,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -6409,10 +6409,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>586360</v>
+        <v>586738</v>
       </c>
       <c r="R54" t="n">
-        <v>7274887</v>
+        <v>7274804</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6481,7 +6481,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121532535</v>
+        <v>121532534</v>
       </c>
       <c r="B55" t="n">
         <v>79697</v>
@@ -6525,10 +6525,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>586434</v>
+        <v>586428</v>
       </c>
       <c r="R55" t="n">
-        <v>7274786</v>
+        <v>7274781</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6560,7 +6560,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6570,7 +6570,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6597,7 +6597,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121533115</v>
+        <v>121533119</v>
       </c>
       <c r="B56" t="n">
         <v>78616</v>
@@ -6641,10 +6641,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>586409</v>
+        <v>586262</v>
       </c>
       <c r="R56" t="n">
-        <v>7274860</v>
+        <v>7274991</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6676,7 +6676,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6686,7 +6686,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6713,10 +6713,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121532630</v>
+        <v>121532535</v>
       </c>
       <c r="B57" t="n">
-        <v>90724</v>
+        <v>79697</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6729,21 +6729,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -6757,10 +6757,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>586738</v>
+        <v>586434</v>
       </c>
       <c r="R57" t="n">
-        <v>7274804</v>
+        <v>7274786</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6792,7 +6792,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6829,10 +6829,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121532532</v>
+        <v>121533188</v>
       </c>
       <c r="B58" t="n">
-        <v>79697</v>
+        <v>82400</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6845,21 +6845,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -6873,10 +6873,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>586670</v>
+        <v>586262</v>
       </c>
       <c r="R58" t="n">
-        <v>7274637</v>
+        <v>7274991</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6908,7 +6908,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7061,10 +7061,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121532446</v>
+        <v>121532533</v>
       </c>
       <c r="B60" t="n">
-        <v>79698</v>
+        <v>79697</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7077,21 +7077,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -7105,10 +7105,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>586289</v>
+        <v>586423</v>
       </c>
       <c r="R60" t="n">
-        <v>7274978</v>
+        <v>7274746</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7140,7 +7140,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7150,7 +7150,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AD60" t="b">

--- a/artfynd/A 31945-2021 artfynd.xlsx
+++ b/artfynd/A 31945-2021 artfynd.xlsx
@@ -4797,10 +4797,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121476719</v>
+        <v>121476790</v>
       </c>
       <c r="B40" t="n">
-        <v>79697</v>
+        <v>78698</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4813,21 +4813,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>864</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4837,10 +4837,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>586424</v>
+        <v>586263</v>
       </c>
       <c r="R40" t="n">
-        <v>7274747</v>
+        <v>7274991</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4899,7 +4899,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121476718</v>
+        <v>121476719</v>
       </c>
       <c r="B41" t="n">
         <v>79697</v>
@@ -4939,10 +4939,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>586671</v>
+        <v>586424</v>
       </c>
       <c r="R41" t="n">
-        <v>7274637</v>
+        <v>7274747</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5001,10 +5001,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121476790</v>
+        <v>121476718</v>
       </c>
       <c r="B42" t="n">
-        <v>78698</v>
+        <v>79697</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5017,21 +5017,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>864</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5041,10 +5041,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>586263</v>
+        <v>586671</v>
       </c>
       <c r="R42" t="n">
-        <v>7274991</v>
+        <v>7274637</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -6249,10 +6249,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121532208</v>
+        <v>121532630</v>
       </c>
       <c r="B53" t="n">
-        <v>91290</v>
+        <v>90724</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6261,25 +6261,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>760</v>
+        <v>1108</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -6293,10 +6293,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>586434</v>
+        <v>586738</v>
       </c>
       <c r="R53" t="n">
-        <v>7274786</v>
+        <v>7274804</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6328,7 +6328,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6338,7 +6338,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6365,10 +6365,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121532630</v>
+        <v>121532208</v>
       </c>
       <c r="B54" t="n">
-        <v>90724</v>
+        <v>91290</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6377,25 +6377,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1108</v>
+        <v>760</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -6409,10 +6409,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>586738</v>
+        <v>586434</v>
       </c>
       <c r="R54" t="n">
-        <v>7274804</v>
+        <v>7274786</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD54" t="b">

--- a/artfynd/A 31945-2021 artfynd.xlsx
+++ b/artfynd/A 31945-2021 artfynd.xlsx
@@ -3267,10 +3267,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121476720</v>
+        <v>121477312</v>
       </c>
       <c r="B25" t="n">
-        <v>79697</v>
+        <v>78616</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3283,21 +3283,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3307,10 +3307,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>586428</v>
+        <v>586774</v>
       </c>
       <c r="R25" t="n">
-        <v>7274782</v>
+        <v>7274818</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3369,10 +3369,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121477312</v>
+        <v>121477385</v>
       </c>
       <c r="B26" t="n">
-        <v>78616</v>
+        <v>82400</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3385,21 +3385,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3409,10 +3409,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>586774</v>
+        <v>586263</v>
       </c>
       <c r="R26" t="n">
-        <v>7274818</v>
+        <v>7274991</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3573,10 +3573,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121476595</v>
+        <v>121476441</v>
       </c>
       <c r="B28" t="n">
-        <v>79698</v>
+        <v>90728</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3589,21 +3589,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>586410</v>
+        <v>586513</v>
       </c>
       <c r="R28" t="n">
-        <v>7274861</v>
+        <v>7275037</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3675,10 +3675,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121476688</v>
+        <v>121476597</v>
       </c>
       <c r="B29" t="n">
-        <v>91014</v>
+        <v>79698</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3691,21 +3691,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3715,10 +3715,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>586513</v>
+        <v>586361</v>
       </c>
       <c r="R29" t="n">
-        <v>7275037</v>
+        <v>7274887</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3777,10 +3777,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121477319</v>
+        <v>121476790</v>
       </c>
       <c r="B30" t="n">
-        <v>78616</v>
+        <v>78698</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3793,21 +3793,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3879,10 +3879,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121476841</v>
+        <v>121476720</v>
       </c>
       <c r="B31" t="n">
-        <v>90724</v>
+        <v>79697</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3895,21 +3895,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3919,10 +3919,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>586739</v>
+        <v>586428</v>
       </c>
       <c r="R31" t="n">
-        <v>7274805</v>
+        <v>7274782</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3981,10 +3981,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121476600</v>
+        <v>121476688</v>
       </c>
       <c r="B32" t="n">
-        <v>79698</v>
+        <v>91014</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3997,21 +3997,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4021,10 +4021,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>586290</v>
+        <v>586513</v>
       </c>
       <c r="R32" t="n">
-        <v>7274978</v>
+        <v>7275037</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4083,10 +4083,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121477385</v>
+        <v>121476439</v>
       </c>
       <c r="B33" t="n">
-        <v>82400</v>
+        <v>90728</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4099,21 +4099,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4123,10 +4123,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>586263</v>
+        <v>586310</v>
       </c>
       <c r="R33" t="n">
-        <v>7274991</v>
+        <v>7274979</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4185,10 +4185,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121476843</v>
+        <v>121476719</v>
       </c>
       <c r="B34" t="n">
-        <v>90724</v>
+        <v>79697</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4201,21 +4201,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4225,10 +4225,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>586373</v>
+        <v>586424</v>
       </c>
       <c r="R34" t="n">
-        <v>7275002</v>
+        <v>7274747</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4287,10 +4287,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121476441</v>
+        <v>121477395</v>
       </c>
       <c r="B35" t="n">
-        <v>90728</v>
+        <v>88046</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4303,21 +4303,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4327,10 +4327,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>586513</v>
+        <v>586434</v>
       </c>
       <c r="R35" t="n">
-        <v>7275037</v>
+        <v>7274787</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4389,10 +4389,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121476721</v>
+        <v>121477319</v>
       </c>
       <c r="B36" t="n">
-        <v>79697</v>
+        <v>78616</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4405,21 +4405,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4429,10 +4429,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>586434</v>
+        <v>586263</v>
       </c>
       <c r="R36" t="n">
-        <v>7274787</v>
+        <v>7274991</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4491,10 +4491,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121476846</v>
+        <v>121476600</v>
       </c>
       <c r="B37" t="n">
-        <v>90724</v>
+        <v>79698</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4507,21 +4507,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4531,10 +4531,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>586623</v>
+        <v>586290</v>
       </c>
       <c r="R37" t="n">
-        <v>7275057</v>
+        <v>7274978</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4593,10 +4593,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121477395</v>
+        <v>121476718</v>
       </c>
       <c r="B38" t="n">
-        <v>88046</v>
+        <v>79697</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4609,21 +4609,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4633,10 +4633,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>586434</v>
+        <v>586671</v>
       </c>
       <c r="R38" t="n">
-        <v>7274787</v>
+        <v>7274637</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4695,10 +4695,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121476439</v>
+        <v>121476721</v>
       </c>
       <c r="B39" t="n">
-        <v>90728</v>
+        <v>79697</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4711,21 +4711,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>586310</v>
+        <v>586434</v>
       </c>
       <c r="R39" t="n">
-        <v>7274979</v>
+        <v>7274787</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4797,10 +4797,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121476790</v>
+        <v>121476841</v>
       </c>
       <c r="B40" t="n">
-        <v>78698</v>
+        <v>90724</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4813,21 +4813,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>864</v>
+        <v>1108</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4837,10 +4837,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>586263</v>
+        <v>586739</v>
       </c>
       <c r="R40" t="n">
-        <v>7274991</v>
+        <v>7274805</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4899,10 +4899,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121476719</v>
+        <v>121476595</v>
       </c>
       <c r="B41" t="n">
-        <v>79697</v>
+        <v>79698</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4915,21 +4915,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4939,10 +4939,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>586424</v>
+        <v>586410</v>
       </c>
       <c r="R41" t="n">
-        <v>7274747</v>
+        <v>7274861</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5001,10 +5001,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121476718</v>
+        <v>121476843</v>
       </c>
       <c r="B42" t="n">
-        <v>79697</v>
+        <v>90724</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5017,21 +5017,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5041,10 +5041,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>586671</v>
+        <v>586373</v>
       </c>
       <c r="R42" t="n">
-        <v>7274637</v>
+        <v>7275002</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5103,10 +5103,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121476597</v>
+        <v>121476846</v>
       </c>
       <c r="B43" t="n">
-        <v>79698</v>
+        <v>90724</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5119,21 +5119,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5143,10 +5143,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>586361</v>
+        <v>586623</v>
       </c>
       <c r="R43" t="n">
-        <v>7274887</v>
+        <v>7275057</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5205,10 +5205,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121533112</v>
+        <v>121532534</v>
       </c>
       <c r="B44" t="n">
-        <v>78616</v>
+        <v>79697</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5221,21 +5221,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5249,10 +5249,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>586773</v>
+        <v>586428</v>
       </c>
       <c r="R44" t="n">
-        <v>7274818</v>
+        <v>7274781</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5321,7 +5321,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121532442</v>
+        <v>121532444</v>
       </c>
       <c r="B45" t="n">
         <v>79698</v>
@@ -5365,10 +5365,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>586409</v>
+        <v>586241</v>
       </c>
       <c r="R45" t="n">
-        <v>7274860</v>
+        <v>7274946</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5400,7 +5400,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5410,7 +5410,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5437,10 +5437,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121533115</v>
+        <v>121532208</v>
       </c>
       <c r="B46" t="n">
-        <v>78616</v>
+        <v>91290</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5449,25 +5449,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5481,10 +5481,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>586409</v>
+        <v>586434</v>
       </c>
       <c r="R46" t="n">
-        <v>7274860</v>
+        <v>7274786</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5553,10 +5553,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121532577</v>
+        <v>121532630</v>
       </c>
       <c r="B47" t="n">
-        <v>78698</v>
+        <v>90724</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5569,21 +5569,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>864</v>
+        <v>1108</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5597,10 +5597,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>586262</v>
+        <v>586738</v>
       </c>
       <c r="R47" t="n">
-        <v>7274991</v>
+        <v>7274804</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5632,7 +5632,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5642,7 +5642,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5669,10 +5669,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121532632</v>
+        <v>121532319</v>
       </c>
       <c r="B48" t="n">
-        <v>90724</v>
+        <v>90728</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5685,21 +5685,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5713,10 +5713,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>586372</v>
+        <v>586310</v>
       </c>
       <c r="R48" t="n">
-        <v>7275002</v>
+        <v>7274978</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5748,7 +5748,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5785,10 +5785,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121532443</v>
+        <v>121533115</v>
       </c>
       <c r="B49" t="n">
-        <v>79698</v>
+        <v>78616</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5801,21 +5801,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5829,10 +5829,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>586360</v>
+        <v>586409</v>
       </c>
       <c r="R49" t="n">
-        <v>7274887</v>
+        <v>7274860</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5864,7 +5864,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5874,7 +5874,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5901,10 +5901,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121532532</v>
+        <v>121533112</v>
       </c>
       <c r="B50" t="n">
-        <v>79697</v>
+        <v>78616</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5917,21 +5917,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5945,10 +5945,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>586670</v>
+        <v>586773</v>
       </c>
       <c r="R50" t="n">
-        <v>7274637</v>
+        <v>7274818</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5980,7 +5980,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5990,7 +5990,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6017,10 +6017,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121532446</v>
+        <v>121532533</v>
       </c>
       <c r="B51" t="n">
-        <v>79698</v>
+        <v>79697</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6033,21 +6033,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -6061,10 +6061,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>586289</v>
+        <v>586423</v>
       </c>
       <c r="R51" t="n">
-        <v>7274978</v>
+        <v>7274746</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6096,7 +6096,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6106,7 +6106,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6133,10 +6133,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121532444</v>
+        <v>121532532</v>
       </c>
       <c r="B52" t="n">
-        <v>79698</v>
+        <v>79697</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6149,21 +6149,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>586241</v>
+        <v>586670</v>
       </c>
       <c r="R52" t="n">
-        <v>7274946</v>
+        <v>7274637</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6212,7 +6212,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6249,10 +6249,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121532630</v>
+        <v>121532446</v>
       </c>
       <c r="B53" t="n">
-        <v>90724</v>
+        <v>79698</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6265,21 +6265,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -6293,10 +6293,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>586738</v>
+        <v>586289</v>
       </c>
       <c r="R53" t="n">
-        <v>7274804</v>
+        <v>7274978</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6328,7 +6328,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6338,7 +6338,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6365,10 +6365,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121532208</v>
+        <v>121532442</v>
       </c>
       <c r="B54" t="n">
-        <v>91290</v>
+        <v>79698</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6377,25 +6377,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>760</v>
+        <v>2081</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -6409,10 +6409,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>586434</v>
+        <v>586409</v>
       </c>
       <c r="R54" t="n">
-        <v>7274786</v>
+        <v>7274860</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6481,10 +6481,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121532534</v>
+        <v>121532443</v>
       </c>
       <c r="B55" t="n">
-        <v>79697</v>
+        <v>79698</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6497,21 +6497,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -6525,10 +6525,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>586428</v>
+        <v>586360</v>
       </c>
       <c r="R55" t="n">
-        <v>7274781</v>
+        <v>7274887</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6560,7 +6560,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6570,7 +6570,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6597,10 +6597,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121533119</v>
+        <v>121532535</v>
       </c>
       <c r="B56" t="n">
-        <v>78616</v>
+        <v>79697</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6613,21 +6613,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -6641,10 +6641,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>586262</v>
+        <v>586434</v>
       </c>
       <c r="R56" t="n">
-        <v>7274991</v>
+        <v>7274786</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6676,7 +6676,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6686,7 +6686,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6713,10 +6713,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121532535</v>
+        <v>121533188</v>
       </c>
       <c r="B57" t="n">
-        <v>79697</v>
+        <v>82400</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6729,21 +6729,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -6757,10 +6757,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>586434</v>
+        <v>586262</v>
       </c>
       <c r="R57" t="n">
-        <v>7274786</v>
+        <v>7274991</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6792,7 +6792,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6829,10 +6829,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121533188</v>
+        <v>121532632</v>
       </c>
       <c r="B58" t="n">
-        <v>82400</v>
+        <v>90724</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6845,21 +6845,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -6873,10 +6873,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>586262</v>
+        <v>586372</v>
       </c>
       <c r="R58" t="n">
-        <v>7274991</v>
+        <v>7275002</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6908,7 +6908,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6945,10 +6945,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121532319</v>
+        <v>121533119</v>
       </c>
       <c r="B59" t="n">
-        <v>90728</v>
+        <v>78616</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6961,21 +6961,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -6989,10 +6989,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>586310</v>
+        <v>586262</v>
       </c>
       <c r="R59" t="n">
-        <v>7274978</v>
+        <v>7274991</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7024,7 +7024,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7061,10 +7061,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121532533</v>
+        <v>121532577</v>
       </c>
       <c r="B60" t="n">
-        <v>79697</v>
+        <v>78698</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7077,21 +7077,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>864</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -7105,10 +7105,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>586423</v>
+        <v>586262</v>
       </c>
       <c r="R60" t="n">
-        <v>7274746</v>
+        <v>7274991</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7140,7 +7140,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7150,7 +7150,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="AD60" t="b">

--- a/artfynd/A 31945-2021 artfynd.xlsx
+++ b/artfynd/A 31945-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY60"/>
+  <dimension ref="A1:AY59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1135,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>95057695</v>
+        <v>95057779</v>
       </c>
       <c r="B6" t="n">
-        <v>78570</v>
+        <v>89388</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,21 +1151,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1176,10 +1176,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>586433.5503060317</v>
+        <v>586558.325778969</v>
       </c>
       <c r="R6" t="n">
-        <v>7274861.375211717</v>
+        <v>7274819.95991541</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1248,10 +1248,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>95057779</v>
+        <v>95057508</v>
       </c>
       <c r="B7" t="n">
-        <v>89388</v>
+        <v>78570</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1264,21 +1264,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1289,10 +1289,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>586558.325778969</v>
+        <v>586362.0241182805</v>
       </c>
       <c r="R7" t="n">
-        <v>7274819.95991541</v>
+        <v>7274910.59102959</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1361,10 +1361,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>95057508</v>
+        <v>95057883</v>
       </c>
       <c r="B8" t="n">
-        <v>78570</v>
+        <v>56395</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,35 +1377,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>586362.0241182805</v>
+        <v>586545.4116660216</v>
       </c>
       <c r="R8" t="n">
-        <v>7274910.59102959</v>
+        <v>7274947.112282317</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1448,6 +1450,11 @@
       <c r="AB8" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,10 +1481,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>95057883</v>
+        <v>95057330</v>
       </c>
       <c r="B9" t="n">
-        <v>56395</v>
+        <v>89406</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,37 +1497,35 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>586545.4116660216</v>
+        <v>586341.9214685706</v>
       </c>
       <c r="R9" t="n">
-        <v>7274947.112282317</v>
+        <v>7274917.446002343</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1563,11 +1568,6 @@
       <c r="AB9" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1594,10 +1594,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>95057330</v>
+        <v>95057491</v>
       </c>
       <c r="B10" t="n">
-        <v>89406</v>
+        <v>89410</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1610,21 +1610,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1707,10 +1707,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>95057491</v>
+        <v>95057697</v>
       </c>
       <c r="B11" t="n">
-        <v>89410</v>
+        <v>77506</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1723,21 +1723,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1748,10 +1748,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>586341.9214685706</v>
+        <v>586433.5503060317</v>
       </c>
       <c r="R11" t="n">
-        <v>7274917.446002343</v>
+        <v>7274861.375211717</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1820,10 +1820,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>95057697</v>
+        <v>95057800</v>
       </c>
       <c r="B12" t="n">
-        <v>77506</v>
+        <v>89673</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1836,21 +1836,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1861,10 +1861,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>586433.5503060317</v>
+        <v>586558.325778969</v>
       </c>
       <c r="R12" t="n">
-        <v>7274861.375211717</v>
+        <v>7274819.95991541</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1933,10 +1933,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>95057800</v>
+        <v>95057959</v>
       </c>
       <c r="B13" t="n">
-        <v>89673</v>
+        <v>89392</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1949,21 +1949,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1974,10 +1974,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>586558.325778969</v>
+        <v>586404.3458425554</v>
       </c>
       <c r="R13" t="n">
-        <v>7274819.95991541</v>
+        <v>7274978.931176641</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2046,10 +2046,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>95057959</v>
+        <v>95057696</v>
       </c>
       <c r="B14" t="n">
-        <v>89392</v>
+        <v>78569</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2062,21 +2062,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>586404.3458425554</v>
+        <v>586433.5503060317</v>
       </c>
       <c r="R14" t="n">
-        <v>7274978.931176641</v>
+        <v>7274861.375211717</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2159,10 +2159,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>95057696</v>
+        <v>95057275</v>
       </c>
       <c r="B15" t="n">
-        <v>78569</v>
+        <v>89673</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2175,21 +2175,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2200,10 +2200,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>586433.5503060317</v>
+        <v>586341.9214685706</v>
       </c>
       <c r="R15" t="n">
-        <v>7274861.375211717</v>
+        <v>7274917.446002343</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2272,10 +2272,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>95057275</v>
+        <v>95057974</v>
       </c>
       <c r="B16" t="n">
-        <v>89673</v>
+        <v>78570</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2288,21 +2288,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2313,10 +2313,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>586341.9214685706</v>
+        <v>586355.7916929023</v>
       </c>
       <c r="R16" t="n">
-        <v>7274917.446002343</v>
+        <v>7275008.540254837</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2385,10 +2385,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>95057974</v>
+        <v>95057483</v>
       </c>
       <c r="B17" t="n">
-        <v>78570</v>
+        <v>85703</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2401,21 +2401,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>510</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2426,10 +2426,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>586355.7916929023</v>
+        <v>586341.9214685706</v>
       </c>
       <c r="R17" t="n">
-        <v>7275008.540254837</v>
+        <v>7274917.446002343</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2498,10 +2498,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>95057483</v>
+        <v>95057270</v>
       </c>
       <c r="B18" t="n">
-        <v>85703</v>
+        <v>89832</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2510,25 +2510,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>510</v>
+        <v>1209</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2611,10 +2611,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>95057270</v>
+        <v>95057616</v>
       </c>
       <c r="B19" t="n">
-        <v>89832</v>
+        <v>78570</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2623,25 +2623,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1209</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2652,10 +2652,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>586341.9214685706</v>
+        <v>586390.5925614857</v>
       </c>
       <c r="R19" t="n">
-        <v>7274917.446002343</v>
+        <v>7274870.033610417</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2724,10 +2724,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>95057616</v>
+        <v>95057648</v>
       </c>
       <c r="B20" t="n">
-        <v>78570</v>
+        <v>78569</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2740,21 +2740,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2837,10 +2837,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>95057648</v>
+        <v>95057933</v>
       </c>
       <c r="B21" t="n">
-        <v>78569</v>
+        <v>89388</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2853,21 +2853,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2878,10 +2878,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>586390.5925614857</v>
+        <v>586570.368125353</v>
       </c>
       <c r="R21" t="n">
-        <v>7274870.033610417</v>
+        <v>7274958.208810494</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2950,10 +2950,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>95057933</v>
+        <v>121477315</v>
       </c>
       <c r="B22" t="n">
-        <v>89388</v>
+        <v>78616</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2966,38 +2966,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sorsele, Ly lm</t>
+          <t>Jiltjaurberget, Ly lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>586570.368125353</v>
+        <v>586410</v>
       </c>
       <c r="R22" t="n">
-        <v>7274958.208810494</v>
+        <v>7274861</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3021,22 +3020,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2021-07-24</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-01-15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2021-07-24</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-01-17</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3051,22 +3040,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Elin Lindmark</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Isak Sarac</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121477315</v>
+        <v>121476598</v>
       </c>
       <c r="B23" t="n">
-        <v>78616</v>
+        <v>79698</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3079,21 +3068,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3103,10 +3092,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>586410</v>
+        <v>586242</v>
       </c>
       <c r="R23" t="n">
-        <v>7274861</v>
+        <v>7274946</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3165,10 +3154,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121476598</v>
+        <v>121477312</v>
       </c>
       <c r="B24" t="n">
-        <v>79698</v>
+        <v>78616</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3181,21 +3170,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3205,10 +3194,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>586242</v>
+        <v>586774</v>
       </c>
       <c r="R24" t="n">
-        <v>7274946</v>
+        <v>7274818</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3267,10 +3256,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121477312</v>
+        <v>121477385</v>
       </c>
       <c r="B25" t="n">
-        <v>78616</v>
+        <v>82400</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3283,21 +3272,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3307,10 +3296,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>586774</v>
+        <v>586263</v>
       </c>
       <c r="R25" t="n">
-        <v>7274818</v>
+        <v>7274991</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3369,10 +3358,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121477385</v>
+        <v>121476521</v>
       </c>
       <c r="B26" t="n">
-        <v>82400</v>
+        <v>79563</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3385,21 +3374,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1312</v>
+        <v>388</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3409,10 +3398,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>586263</v>
+        <v>586320</v>
       </c>
       <c r="R26" t="n">
-        <v>7274991</v>
+        <v>7274981</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3471,10 +3460,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121476521</v>
+        <v>121476597</v>
       </c>
       <c r="B27" t="n">
-        <v>79563</v>
+        <v>79698</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3487,21 +3476,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>388</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3511,10 +3500,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>586320</v>
+        <v>586361</v>
       </c>
       <c r="R27" t="n">
-        <v>7274981</v>
+        <v>7274887</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3573,10 +3562,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121476597</v>
+        <v>121476441</v>
       </c>
       <c r="B28" t="n">
-        <v>79698</v>
+        <v>90728</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3589,21 +3578,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3613,10 +3602,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>586361</v>
+        <v>586513</v>
       </c>
       <c r="R28" t="n">
-        <v>7274887</v>
+        <v>7275037</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3675,10 +3664,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121476441</v>
+        <v>121476720</v>
       </c>
       <c r="B29" t="n">
-        <v>90728</v>
+        <v>79697</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3691,21 +3680,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3715,10 +3704,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>586513</v>
+        <v>586428</v>
       </c>
       <c r="R29" t="n">
-        <v>7275037</v>
+        <v>7274782</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3777,10 +3766,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121476720</v>
+        <v>121476790</v>
       </c>
       <c r="B30" t="n">
-        <v>79697</v>
+        <v>78698</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3793,21 +3782,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>864</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3817,10 +3806,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>586428</v>
+        <v>586263</v>
       </c>
       <c r="R30" t="n">
-        <v>7274782</v>
+        <v>7274991</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3879,10 +3868,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121476790</v>
+        <v>121476688</v>
       </c>
       <c r="B31" t="n">
-        <v>78698</v>
+        <v>91014</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3895,21 +3884,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>864</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3919,10 +3908,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>586263</v>
+        <v>586513</v>
       </c>
       <c r="R31" t="n">
-        <v>7274991</v>
+        <v>7275037</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3981,10 +3970,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121476688</v>
+        <v>121476439</v>
       </c>
       <c r="B32" t="n">
-        <v>91014</v>
+        <v>90728</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3997,21 +3986,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4021,10 +4010,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>586513</v>
+        <v>586310</v>
       </c>
       <c r="R32" t="n">
-        <v>7275037</v>
+        <v>7274979</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4083,10 +4072,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121476439</v>
+        <v>121476719</v>
       </c>
       <c r="B33" t="n">
-        <v>90728</v>
+        <v>79697</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4099,21 +4088,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4123,10 +4112,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>586310</v>
+        <v>586424</v>
       </c>
       <c r="R33" t="n">
-        <v>7274979</v>
+        <v>7274747</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4185,10 +4174,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121476719</v>
+        <v>121477395</v>
       </c>
       <c r="B34" t="n">
-        <v>79697</v>
+        <v>88046</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4201,21 +4190,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4225,10 +4214,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>586424</v>
+        <v>586434</v>
       </c>
       <c r="R34" t="n">
-        <v>7274747</v>
+        <v>7274787</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4287,10 +4276,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121477395</v>
+        <v>121477319</v>
       </c>
       <c r="B35" t="n">
-        <v>88046</v>
+        <v>78616</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4303,21 +4292,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4327,10 +4316,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>586434</v>
+        <v>586263</v>
       </c>
       <c r="R35" t="n">
-        <v>7274787</v>
+        <v>7274991</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4389,10 +4378,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121477319</v>
+        <v>121476600</v>
       </c>
       <c r="B36" t="n">
-        <v>78616</v>
+        <v>79698</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4405,21 +4394,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4429,10 +4418,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>586263</v>
+        <v>586290</v>
       </c>
       <c r="R36" t="n">
-        <v>7274991</v>
+        <v>7274978</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4491,10 +4480,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121476600</v>
+        <v>121476718</v>
       </c>
       <c r="B37" t="n">
-        <v>79698</v>
+        <v>79697</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4507,21 +4496,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4531,10 +4520,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>586290</v>
+        <v>586671</v>
       </c>
       <c r="R37" t="n">
-        <v>7274978</v>
+        <v>7274637</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4593,7 +4582,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121476718</v>
+        <v>121476721</v>
       </c>
       <c r="B38" t="n">
         <v>79697</v>
@@ -4633,10 +4622,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>586671</v>
+        <v>586434</v>
       </c>
       <c r="R38" t="n">
-        <v>7274637</v>
+        <v>7274787</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4695,10 +4684,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121476721</v>
+        <v>121476841</v>
       </c>
       <c r="B39" t="n">
-        <v>79697</v>
+        <v>90724</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4711,21 +4700,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4735,10 +4724,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>586434</v>
+        <v>586739</v>
       </c>
       <c r="R39" t="n">
-        <v>7274787</v>
+        <v>7274805</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4797,10 +4786,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121476841</v>
+        <v>121476595</v>
       </c>
       <c r="B40" t="n">
-        <v>90724</v>
+        <v>79698</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4813,21 +4802,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4837,10 +4826,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>586739</v>
+        <v>586410</v>
       </c>
       <c r="R40" t="n">
-        <v>7274805</v>
+        <v>7274861</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4899,10 +4888,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121476595</v>
+        <v>121476846</v>
       </c>
       <c r="B41" t="n">
-        <v>79698</v>
+        <v>90724</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4915,21 +4904,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4939,10 +4928,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>586410</v>
+        <v>586623</v>
       </c>
       <c r="R41" t="n">
-        <v>7274861</v>
+        <v>7275057</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5001,7 +4990,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121476846</v>
+        <v>121476843</v>
       </c>
       <c r="B42" t="n">
         <v>90724</v>
@@ -5041,10 +5030,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>586623</v>
+        <v>586373</v>
       </c>
       <c r="R42" t="n">
-        <v>7275057</v>
+        <v>7275002</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5103,10 +5092,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121476843</v>
+        <v>121532319</v>
       </c>
       <c r="B43" t="n">
-        <v>90724</v>
+        <v>90728</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5119,34 +5108,38 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Jiltjaurberget, Ly lm</t>
+          <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>586373</v>
+        <v>586310</v>
       </c>
       <c r="R43" t="n">
-        <v>7275002</v>
+        <v>7274978</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5173,12 +5166,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2020-01-15</t>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2020-01-17</t>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5193,22 +5196,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Elin Lindmark</t>
+          <t>Max Jonsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Isak Sarac</t>
+          <t>Max Jonsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121532319</v>
+        <v>121533115</v>
       </c>
       <c r="B44" t="n">
-        <v>90728</v>
+        <v>78616</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5221,21 +5224,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5249,10 +5252,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>586310</v>
+        <v>586409</v>
       </c>
       <c r="R44" t="n">
-        <v>7274978</v>
+        <v>7274860</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5284,7 +5287,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5294,7 +5297,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5321,10 +5324,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121533115</v>
+        <v>121532442</v>
       </c>
       <c r="B45" t="n">
-        <v>78616</v>
+        <v>79698</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5337,21 +5340,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5400,7 +5403,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5410,7 +5413,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5437,10 +5440,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121532442</v>
+        <v>121532577</v>
       </c>
       <c r="B46" t="n">
-        <v>79698</v>
+        <v>78698</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5453,21 +5456,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5481,10 +5484,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>586409</v>
+        <v>586262</v>
       </c>
       <c r="R46" t="n">
-        <v>7274860</v>
+        <v>7274991</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5516,7 +5519,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5526,7 +5529,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5553,10 +5556,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121532577</v>
+        <v>121532535</v>
       </c>
       <c r="B47" t="n">
-        <v>78698</v>
+        <v>79697</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5569,21 +5572,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>864</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5597,10 +5600,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>586262</v>
+        <v>586434</v>
       </c>
       <c r="R47" t="n">
-        <v>7274991</v>
+        <v>7274786</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5632,7 +5635,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5642,7 +5645,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5669,10 +5672,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121532535</v>
+        <v>121533188</v>
       </c>
       <c r="B48" t="n">
-        <v>79697</v>
+        <v>82400</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5685,21 +5688,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5713,10 +5716,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>586434</v>
+        <v>586262</v>
       </c>
       <c r="R48" t="n">
-        <v>7274786</v>
+        <v>7274991</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5748,7 +5751,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5758,7 +5761,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5785,10 +5788,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121533188</v>
+        <v>121532532</v>
       </c>
       <c r="B49" t="n">
-        <v>82400</v>
+        <v>79697</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5801,21 +5804,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5829,10 +5832,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>586262</v>
+        <v>586670</v>
       </c>
       <c r="R49" t="n">
-        <v>7274991</v>
+        <v>7274637</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5864,7 +5867,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5874,7 +5877,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5901,10 +5904,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121532532</v>
+        <v>121532630</v>
       </c>
       <c r="B50" t="n">
-        <v>79697</v>
+        <v>90724</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5917,21 +5920,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5945,10 +5948,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>586670</v>
+        <v>586738</v>
       </c>
       <c r="R50" t="n">
-        <v>7274637</v>
+        <v>7274804</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5980,7 +5983,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5990,7 +5993,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6017,10 +6020,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121532630</v>
+        <v>121532534</v>
       </c>
       <c r="B51" t="n">
-        <v>90724</v>
+        <v>79697</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6033,21 +6036,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -6061,10 +6064,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>586738</v>
+        <v>586428</v>
       </c>
       <c r="R51" t="n">
-        <v>7274804</v>
+        <v>7274781</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6096,7 +6099,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6106,7 +6109,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6133,10 +6136,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121532534</v>
+        <v>121533119</v>
       </c>
       <c r="B52" t="n">
-        <v>79697</v>
+        <v>78616</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6149,21 +6152,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -6177,10 +6180,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>586428</v>
+        <v>586262</v>
       </c>
       <c r="R52" t="n">
-        <v>7274781</v>
+        <v>7274991</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6212,7 +6215,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6222,7 +6225,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6249,10 +6252,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121533119</v>
+        <v>121532444</v>
       </c>
       <c r="B53" t="n">
-        <v>78616</v>
+        <v>79698</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6265,21 +6268,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -6293,10 +6296,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>586262</v>
+        <v>586241</v>
       </c>
       <c r="R53" t="n">
-        <v>7274991</v>
+        <v>7274946</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6328,7 +6331,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6338,7 +6341,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6365,7 +6368,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121532444</v>
+        <v>121532446</v>
       </c>
       <c r="B54" t="n">
         <v>79698</v>
@@ -6409,10 +6412,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>586241</v>
+        <v>586289</v>
       </c>
       <c r="R54" t="n">
-        <v>7274946</v>
+        <v>7274978</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6444,7 +6447,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6454,7 +6457,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6481,7 +6484,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121532446</v>
+        <v>121532443</v>
       </c>
       <c r="B55" t="n">
         <v>79698</v>
@@ -6525,10 +6528,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>586289</v>
+        <v>586360</v>
       </c>
       <c r="R55" t="n">
-        <v>7274978</v>
+        <v>7274887</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6560,7 +6563,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6570,7 +6573,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6597,10 +6600,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121532443</v>
+        <v>121533112</v>
       </c>
       <c r="B56" t="n">
-        <v>79698</v>
+        <v>78616</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6613,21 +6616,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -6641,10 +6644,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>586360</v>
+        <v>586773</v>
       </c>
       <c r="R56" t="n">
-        <v>7274887</v>
+        <v>7274818</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6676,7 +6679,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6686,7 +6689,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6713,10 +6716,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121533112</v>
+        <v>121532533</v>
       </c>
       <c r="B57" t="n">
-        <v>78616</v>
+        <v>79697</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6729,21 +6732,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -6757,10 +6760,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>586773</v>
+        <v>586423</v>
       </c>
       <c r="R57" t="n">
-        <v>7274818</v>
+        <v>7274746</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6792,7 +6795,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6802,7 +6805,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6829,10 +6832,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121532533</v>
+        <v>121532632</v>
       </c>
       <c r="B58" t="n">
-        <v>79697</v>
+        <v>90724</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6845,21 +6848,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -6873,10 +6876,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>586423</v>
+        <v>586372</v>
       </c>
       <c r="R58" t="n">
-        <v>7274746</v>
+        <v>7275002</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6908,7 +6911,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6918,7 +6921,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6945,10 +6948,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121532632</v>
+        <v>121532208</v>
       </c>
       <c r="B59" t="n">
-        <v>90724</v>
+        <v>91290</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6957,25 +6960,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1108</v>
+        <v>760</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -6989,10 +6992,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>586372</v>
+        <v>586434</v>
       </c>
       <c r="R59" t="n">
-        <v>7275002</v>
+        <v>7274786</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7024,7 +7027,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7034,7 +7037,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7058,122 +7061,6 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>121532208</v>
-      </c>
-      <c r="B60" t="n">
-        <v>91290</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E60" t="n">
-        <v>760</v>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Doftticka</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Haploporus odorus</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>Sorsele, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q60" t="n">
-        <v>586434</v>
-      </c>
-      <c r="R60" t="n">
-        <v>7274786</v>
-      </c>
-      <c r="S60" t="n">
-        <v>10</v>
-      </c>
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W60" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="Y60" t="inlineStr">
-        <is>
-          <t>2021-05-05</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AA60" t="inlineStr">
-        <is>
-          <t>2021-05-05</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AD60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT60" t="inlineStr"/>
-      <c r="AW60" t="inlineStr">
-        <is>
-          <t>Max Jonsson</t>
-        </is>
-      </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>Max Jonsson</t>
-        </is>
-      </c>
-      <c r="AY60" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31945-2021 artfynd.xlsx
+++ b/artfynd/A 31945-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY59"/>
+  <dimension ref="A1:AY68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>95057489</v>
+        <v>121476521</v>
       </c>
       <c r="B2" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80298</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,38 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>388</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sorsele, Ly lm</t>
+          <t>Jiltjaurberget, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>586341.9214685706</v>
+        <v>586320</v>
       </c>
       <c r="R2" t="n">
-        <v>7274917.446002343</v>
+        <v>7274981</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-07-24</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-01-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-07-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-01-17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,66 +760,60 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Elin Lindmark</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Isak Sarac</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>95057706</v>
+        <v>121476748</v>
       </c>
       <c r="B3" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78686</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sorsele, Ly lm</t>
+          <t>Jiltjaurberget, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>586432.7219169593</v>
+        <v>586800</v>
       </c>
       <c r="R3" t="n">
-        <v>7274861.350529569</v>
+        <v>7274861</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -859,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-07-24</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-01-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-07-24</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-01-17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,66 +857,64 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Elin Lindmark</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Isak Sarac</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>95057960</v>
+        <v>121532196</v>
       </c>
       <c r="B4" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78686</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>586404.3458425554</v>
+        <v>586799</v>
       </c>
       <c r="R4" t="n">
-        <v>7274978.931176641</v>
+        <v>7274861</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,22 +938,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-07-24</t>
+          <t>2021-05-05</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-07-24</t>
+          <t>2021-05-05</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,27 +968,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Max Jonsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Max Jonsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>95057551</v>
+        <v>95057483</v>
       </c>
       <c r="B5" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1030,38 +991,35 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>586390.5925614857</v>
+        <v>586342</v>
       </c>
       <c r="R5" t="n">
-        <v>7274870.033610417</v>
+        <v>7274917</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,24 +1049,9 @@
           <t>2021-07-24</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-07-24</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,15 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>95057779</v>
+        <v>121477395</v>
       </c>
       <c r="B6" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1151,38 +1089,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>510</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sorsele, Ly lm</t>
+          <t>Jiltjaurberget, Ly lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>586558.325778969</v>
+        <v>586434</v>
       </c>
       <c r="R6" t="n">
-        <v>7274819.95991541</v>
+        <v>7274787</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1206,22 +1143,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-07-24</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-01-15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-07-24</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-01-17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1236,27 +1163,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Elin Lindmark</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Isak Sarac</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>95057508</v>
+        <v>121477407</v>
       </c>
       <c r="B7" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1264,38 +1186,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>510</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sorsele, Ly lm</t>
+          <t>Jiltjaurberget, Ly lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>586362.0241182805</v>
+        <v>586336</v>
       </c>
       <c r="R7" t="n">
-        <v>7274910.59102959</v>
+        <v>7274801</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1319,22 +1240,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-07-24</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-01-15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-07-24</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-01-17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1349,27 +1260,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Elin Lindmark</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Isak Sarac</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>95057883</v>
+        <v>121533208</v>
       </c>
       <c r="B8" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,40 +1283,41 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>586545.4116660216</v>
+        <v>586335</v>
       </c>
       <c r="R8" t="n">
-        <v>7274947.112282317</v>
+        <v>7274801</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1434,27 +1341,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-07-24</t>
+          <t>2021-05-05</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-07-24</t>
+          <t>2021-05-05</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,27 +1371,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Max Jonsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Max Jonsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>95057330</v>
+        <v>95057275</v>
       </c>
       <c r="B9" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1497,21 +1394,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1522,10 +1419,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>586341.9214685706</v>
+        <v>586342</v>
       </c>
       <c r="R9" t="n">
-        <v>7274917.446002343</v>
+        <v>7274917</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1555,19 +1452,9 @@
           <t>2021-07-24</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2021-07-24</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1594,15 +1481,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>95057491</v>
+        <v>95057800</v>
       </c>
       <c r="B10" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1610,21 +1492,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1635,10 +1517,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>586341.9214685706</v>
+        <v>586558</v>
       </c>
       <c r="R10" t="n">
-        <v>7274917.446002343</v>
+        <v>7274820</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1668,19 +1550,9 @@
           <t>2021-07-24</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2021-07-24</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1707,15 +1579,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>95057697</v>
+        <v>95057960</v>
       </c>
       <c r="B11" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1723,21 +1590,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1748,10 +1615,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>586433.5503060317</v>
+        <v>586404</v>
       </c>
       <c r="R11" t="n">
-        <v>7274861.375211717</v>
+        <v>7274979</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1781,19 +1648,9 @@
           <t>2021-07-24</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2021-07-24</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1820,15 +1677,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>95057800</v>
+        <v>121476688</v>
       </c>
       <c r="B12" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1845,29 +1697,28 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sorsele, Ly lm</t>
+          <t>Jiltjaurberget, Ly lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>586558.325778969</v>
+        <v>586513</v>
       </c>
       <c r="R12" t="n">
-        <v>7274819.95991541</v>
+        <v>7275037</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1891,22 +1742,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2021-07-24</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-01-15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2021-07-24</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-01-17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1921,66 +1762,64 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Elin Lindmark</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Isak Sarac</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>95057959</v>
+        <v>121532208</v>
       </c>
       <c r="B13" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>760</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>586404.3458425554</v>
+        <v>586434</v>
       </c>
       <c r="R13" t="n">
-        <v>7274978.931176641</v>
+        <v>7274786</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2004,22 +1843,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2021-07-24</t>
+          <t>2021-05-05</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2021-07-24</t>
+          <t>2021-05-05</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2034,27 +1873,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Max Jonsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Max Jonsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>95057696</v>
+        <v>121476790</v>
       </c>
       <c r="B14" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2062,38 +1896,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>864</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sorsele, Ly lm</t>
+          <t>Jiltjaurberget, Ly lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>586433.5503060317</v>
+        <v>586263</v>
       </c>
       <c r="R14" t="n">
-        <v>7274861.375211717</v>
+        <v>7274991</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2117,22 +1950,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2021-07-24</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-01-15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2021-07-24</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-01-17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2147,27 +1970,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Elin Lindmark</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Isak Sarac</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>95057275</v>
+        <v>121532577</v>
       </c>
       <c r="B15" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2175,38 +1993,41 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>864</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>586341.9214685706</v>
+        <v>586262</v>
       </c>
       <c r="R15" t="n">
-        <v>7274917.446002343</v>
+        <v>7274991</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2230,22 +2051,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2021-07-24</t>
+          <t>2021-05-05</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2021-07-24</t>
+          <t>2021-05-05</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2260,49 +2081,44 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Max Jonsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Max Jonsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>95057974</v>
+        <v>95057813</v>
       </c>
       <c r="B16" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92721</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>918</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2313,10 +2129,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>586355.7916929023</v>
+        <v>586581</v>
       </c>
       <c r="R16" t="n">
-        <v>7275008.540254837</v>
+        <v>7274810</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2346,19 +2162,9 @@
           <t>2021-07-24</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2021-07-24</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2385,15 +2191,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>95057483</v>
+        <v>95057489</v>
       </c>
       <c r="B17" t="n">
-        <v>85703</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2401,21 +2202,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>510</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2426,10 +2227,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>586341.9214685706</v>
+        <v>586342</v>
       </c>
       <c r="R17" t="n">
-        <v>7274917.446002343</v>
+        <v>7274917</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2459,19 +2260,9 @@
           <t>2021-07-24</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2021-07-24</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2498,37 +2289,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>95057270</v>
+        <v>95057779</v>
       </c>
       <c r="B18" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1209</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2539,10 +2325,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>586341.9214685706</v>
+        <v>586558</v>
       </c>
       <c r="R18" t="n">
-        <v>7274917.446002343</v>
+        <v>7274820</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2572,19 +2358,9 @@
           <t>2021-07-24</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2021-07-24</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2611,15 +2387,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>95057616</v>
+        <v>95057933</v>
       </c>
       <c r="B19" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2627,21 +2398,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2652,10 +2423,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>586390.5925614857</v>
+        <v>586571</v>
       </c>
       <c r="R19" t="n">
-        <v>7274870.033610417</v>
+        <v>7274959</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2685,19 +2456,9 @@
           <t>2021-07-24</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2021-07-24</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2724,15 +2485,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>95057648</v>
+        <v>121476841</v>
       </c>
       <c r="B20" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2740,38 +2496,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sorsele, Ly lm</t>
+          <t>Jiltjaurberget, Ly lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>586390.5925614857</v>
+        <v>586739</v>
       </c>
       <c r="R20" t="n">
-        <v>7274870.033610417</v>
+        <v>7274805</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2795,22 +2550,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2021-07-24</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-01-15</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2021-07-24</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-01-17</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2825,27 +2570,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Elin Lindmark</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Isak Sarac</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>95057933</v>
+        <v>121476843</v>
       </c>
       <c r="B21" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2871,20 +2611,19 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sorsele, Ly lm</t>
+          <t>Jiltjaurberget, Ly lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>586570.368125353</v>
+        <v>586373</v>
       </c>
       <c r="R21" t="n">
-        <v>7274958.208810494</v>
+        <v>7275002</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2908,22 +2647,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2021-07-24</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-01-15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2021-07-24</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-01-17</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2938,27 +2667,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Elin Lindmark</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Isak Sarac</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121477315</v>
+        <v>121476846</v>
       </c>
       <c r="B22" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2966,21 +2690,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2990,10 +2714,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>586410</v>
+        <v>586623</v>
       </c>
       <c r="R22" t="n">
-        <v>7274861</v>
+        <v>7275057</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3052,15 +2776,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121476598</v>
+        <v>121532630</v>
       </c>
       <c r="B23" t="n">
-        <v>79698</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3068,34 +2787,38 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Jiltjaurberget, Ly lm</t>
+          <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>586242</v>
+        <v>586738</v>
       </c>
       <c r="R23" t="n">
-        <v>7274946</v>
+        <v>7274804</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3122,12 +2845,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2020-01-15</t>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>01:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2020-01-17</t>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>01:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3142,27 +2875,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Elin Lindmark</t>
+          <t>Max Jonsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Isak Sarac</t>
+          <t>Max Jonsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121477312</v>
+        <v>121532632</v>
       </c>
       <c r="B24" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3170,34 +2898,38 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Jiltjaurberget, Ly lm</t>
+          <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>586774</v>
+        <v>586372</v>
       </c>
       <c r="R24" t="n">
-        <v>7274818</v>
+        <v>7275002</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3224,12 +2956,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2020-01-15</t>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2020-01-17</t>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3244,27 +2986,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Elin Lindmark</t>
+          <t>Max Jonsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Isak Sarac</t>
+          <t>Max Jonsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121477385</v>
+        <v>95057959</v>
       </c>
       <c r="B25" t="n">
-        <v>82400</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3272,37 +3009,38 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Jiltjaurberget, Ly lm</t>
+          <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>586263</v>
+        <v>586404</v>
       </c>
       <c r="R25" t="n">
-        <v>7274991</v>
+        <v>7274979</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3326,12 +3064,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2020-01-15</t>
+          <t>2021-07-24</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2020-01-17</t>
+          <t>2021-07-24</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3346,27 +3084,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Elin Lindmark</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Isak Sarac</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121476521</v>
+        <v>121476439</v>
       </c>
       <c r="B26" t="n">
-        <v>79563</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3374,21 +3107,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>388</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3398,10 +3131,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>586320</v>
+        <v>586310</v>
       </c>
       <c r="R26" t="n">
-        <v>7274981</v>
+        <v>7274979</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3460,15 +3193,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121476597</v>
+        <v>121476441</v>
       </c>
       <c r="B27" t="n">
-        <v>79698</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3476,21 +3204,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3500,10 +3228,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>586361</v>
+        <v>586513</v>
       </c>
       <c r="R27" t="n">
-        <v>7274887</v>
+        <v>7275037</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3562,15 +3290,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121476441</v>
+        <v>121532319</v>
       </c>
       <c r="B28" t="n">
-        <v>90728</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3595,17 +3318,21 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Jiltjaurberget, Ly lm</t>
+          <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>586513</v>
+        <v>586310</v>
       </c>
       <c r="R28" t="n">
-        <v>7275037</v>
+        <v>7274978</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3632,12 +3359,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2020-01-15</t>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2020-01-17</t>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3652,65 +3389,61 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Elin Lindmark</t>
+          <t>Max Jonsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Isak Sarac</t>
+          <t>Max Jonsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121476720</v>
+        <v>95057330</v>
       </c>
       <c r="B29" t="n">
-        <v>79697</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Jiltjaurberget, Ly lm</t>
+          <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>586428</v>
+        <v>586342</v>
       </c>
       <c r="R29" t="n">
-        <v>7274782</v>
+        <v>7274917</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3734,12 +3467,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2020-01-15</t>
+          <t>2021-07-24</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2020-01-17</t>
+          <t>2021-07-24</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3754,27 +3487,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Elin Lindmark</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Isak Sarac</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121476790</v>
+        <v>95057270</v>
       </c>
       <c r="B30" t="n">
-        <v>78698</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3782,37 +3510,38 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>864</v>
+        <v>1209</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Jiltjaurberget, Ly lm</t>
+          <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>586263</v>
+        <v>586342</v>
       </c>
       <c r="R30" t="n">
-        <v>7274991</v>
+        <v>7274917</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3836,12 +3565,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2020-01-15</t>
+          <t>2021-07-24</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2020-01-17</t>
+          <t>2021-07-24</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3856,27 +3585,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Elin Lindmark</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Isak Sarac</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121476688</v>
+        <v>121477385</v>
       </c>
       <c r="B31" t="n">
-        <v>91014</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3884,21 +3608,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3908,10 +3632,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>586513</v>
+        <v>586263</v>
       </c>
       <c r="R31" t="n">
-        <v>7275037</v>
+        <v>7274991</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3970,15 +3694,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121476439</v>
+        <v>121533188</v>
       </c>
       <c r="B32" t="n">
-        <v>90728</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3986,34 +3705,38 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Jiltjaurberget, Ly lm</t>
+          <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>586310</v>
+        <v>586262</v>
       </c>
       <c r="R32" t="n">
-        <v>7274979</v>
+        <v>7274991</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4040,12 +3763,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2020-01-15</t>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2020-01-17</t>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4060,27 +3793,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Elin Lindmark</t>
+          <t>Max Jonsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Isak Sarac</t>
+          <t>Max Jonsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121476719</v>
+        <v>95057508</v>
       </c>
       <c r="B33" t="n">
-        <v>79697</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4088,37 +3816,38 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Jiltjaurberget, Ly lm</t>
+          <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>586424</v>
+        <v>586362</v>
       </c>
       <c r="R33" t="n">
-        <v>7274747</v>
+        <v>7274910</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4142,12 +3871,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2020-01-15</t>
+          <t>2021-07-24</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2020-01-17</t>
+          <t>2021-07-24</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4162,27 +3891,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Elin Lindmark</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Isak Sarac</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121477395</v>
+        <v>95057616</v>
       </c>
       <c r="B34" t="n">
-        <v>88046</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4190,37 +3914,38 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>510</v>
+        <v>2081</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Jiltjaurberget, Ly lm</t>
+          <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>586434</v>
+        <v>586391</v>
       </c>
       <c r="R34" t="n">
-        <v>7274787</v>
+        <v>7274870</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4244,12 +3969,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2020-01-15</t>
+          <t>2021-07-24</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2020-01-17</t>
+          <t>2021-07-24</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4264,27 +3989,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Elin Lindmark</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Isak Sarac</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121477319</v>
+        <v>95057695</v>
       </c>
       <c r="B35" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4292,37 +4012,38 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Jiltjaurberget, Ly lm</t>
+          <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>586263</v>
+        <v>586434</v>
       </c>
       <c r="R35" t="n">
-        <v>7274991</v>
+        <v>7274861</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4346,12 +4067,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2020-01-15</t>
+          <t>2021-07-24</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2020-01-17</t>
+          <t>2021-07-24</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4366,27 +4087,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Elin Lindmark</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Isak Sarac</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121476600</v>
+        <v>95057706</v>
       </c>
       <c r="B36" t="n">
-        <v>79698</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4412,19 +4128,20 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Jiltjaurberget, Ly lm</t>
+          <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>586290</v>
+        <v>586433</v>
       </c>
       <c r="R36" t="n">
-        <v>7274978</v>
+        <v>7274862</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4448,12 +4165,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2020-01-15</t>
+          <t>2021-07-24</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2020-01-17</t>
+          <t>2021-07-24</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4468,27 +4185,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Elin Lindmark</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Isak Sarac</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121476718</v>
+        <v>95057974</v>
       </c>
       <c r="B37" t="n">
-        <v>79697</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4496,37 +4208,38 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Jiltjaurberget, Ly lm</t>
+          <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>586671</v>
+        <v>586355</v>
       </c>
       <c r="R37" t="n">
-        <v>7274637</v>
+        <v>7275008</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4550,12 +4263,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2020-01-15</t>
+          <t>2021-07-24</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2020-01-17</t>
+          <t>2021-07-24</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4570,27 +4283,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Elin Lindmark</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Isak Sarac</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121476721</v>
+        <v>121476594</v>
       </c>
       <c r="B38" t="n">
-        <v>79697</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4598,21 +4306,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4622,10 +4330,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>586434</v>
+        <v>586336</v>
       </c>
       <c r="R38" t="n">
-        <v>7274787</v>
+        <v>7274790</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4684,15 +4392,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121476841</v>
+        <v>121476595</v>
       </c>
       <c r="B39" t="n">
-        <v>90724</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4700,21 +4403,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4724,10 +4427,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>586739</v>
+        <v>586410</v>
       </c>
       <c r="R39" t="n">
-        <v>7274805</v>
+        <v>7274861</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4786,15 +4489,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121476595</v>
+        <v>121476597</v>
       </c>
       <c r="B40" t="n">
-        <v>79698</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4826,10 +4524,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>586410</v>
+        <v>586361</v>
       </c>
       <c r="R40" t="n">
-        <v>7274861</v>
+        <v>7274887</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4888,15 +4586,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121476846</v>
+        <v>121476598</v>
       </c>
       <c r="B41" t="n">
-        <v>90724</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4904,21 +4597,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4928,10 +4621,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>586623</v>
+        <v>586242</v>
       </c>
       <c r="R41" t="n">
-        <v>7275057</v>
+        <v>7274946</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4990,15 +4683,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121476843</v>
+        <v>121476600</v>
       </c>
       <c r="B42" t="n">
-        <v>90724</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5006,21 +4694,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5030,10 +4718,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>586373</v>
+        <v>586290</v>
       </c>
       <c r="R42" t="n">
-        <v>7275002</v>
+        <v>7274978</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5092,15 +4780,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121532319</v>
+        <v>121532441</v>
       </c>
       <c r="B43" t="n">
-        <v>90728</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5108,21 +4791,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -5136,10 +4819,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>586310</v>
+        <v>586335</v>
       </c>
       <c r="R43" t="n">
-        <v>7274978</v>
+        <v>7274790</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5171,7 +4854,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5181,7 +4864,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5208,15 +4891,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121533115</v>
+        <v>121532442</v>
       </c>
       <c r="B44" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5224,21 +4902,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5287,7 +4965,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5297,7 +4975,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5324,15 +5002,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121532442</v>
+        <v>121532443</v>
       </c>
       <c r="B45" t="n">
-        <v>79698</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5368,10 +5041,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>586409</v>
+        <v>586360</v>
       </c>
       <c r="R45" t="n">
-        <v>7274860</v>
+        <v>7274887</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5403,7 +5076,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5413,7 +5086,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5440,15 +5113,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121532577</v>
+        <v>121532444</v>
       </c>
       <c r="B46" t="n">
-        <v>78698</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5456,21 +5124,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5484,10 +5152,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>586262</v>
+        <v>586241</v>
       </c>
       <c r="R46" t="n">
-        <v>7274991</v>
+        <v>7274946</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5519,7 +5187,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5529,7 +5197,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5556,15 +5224,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121532535</v>
+        <v>121532446</v>
       </c>
       <c r="B47" t="n">
-        <v>79697</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5572,21 +5235,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5600,10 +5263,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>586434</v>
+        <v>586289</v>
       </c>
       <c r="R47" t="n">
-        <v>7274786</v>
+        <v>7274978</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5635,7 +5298,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5645,7 +5308,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5672,57 +5335,49 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121533188</v>
+        <v>95057697</v>
       </c>
       <c r="B48" t="n">
-        <v>82400</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>586262</v>
+        <v>586434</v>
       </c>
       <c r="R48" t="n">
-        <v>7274991</v>
+        <v>7274861</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5746,22 +5401,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2021-05-05</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>04:00</t>
+          <t>2021-07-24</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2021-05-05</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>04:00</t>
+          <t>2021-07-24</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5776,66 +5421,57 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Max Jonsson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Max Jonsson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121532532</v>
+        <v>121477307</v>
       </c>
       <c r="B49" t="n">
-        <v>79697</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Sorsele, Ly lm</t>
+          <t>Jiltjaurberget, Ly lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>586670</v>
+        <v>586385</v>
       </c>
       <c r="R49" t="n">
-        <v>7274637</v>
+        <v>7274745</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5862,22 +5498,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2021-05-05</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>21:00</t>
+          <t>2020-01-15</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2021-05-05</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>21:00</t>
+          <t>2020-01-17</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5892,66 +5518,57 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Max Jonsson</t>
+          <t>Elin Lindmark</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Max Jonsson</t>
+          <t>Isak Sarac</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121532630</v>
+        <v>121477312</v>
       </c>
       <c r="B50" t="n">
-        <v>90724</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Sorsele, Ly lm</t>
+          <t>Jiltjaurberget, Ly lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>586738</v>
+        <v>586774</v>
       </c>
       <c r="R50" t="n">
-        <v>7274804</v>
+        <v>7274818</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5978,22 +5595,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2021-05-05</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>01:00</t>
+          <t>2020-01-15</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2021-05-05</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>01:00</t>
+          <t>2020-01-17</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6008,66 +5615,57 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Max Jonsson</t>
+          <t>Elin Lindmark</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Max Jonsson</t>
+          <t>Isak Sarac</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121532534</v>
+        <v>121477315</v>
       </c>
       <c r="B51" t="n">
-        <v>79697</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Sorsele, Ly lm</t>
+          <t>Jiltjaurberget, Ly lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>586428</v>
+        <v>586410</v>
       </c>
       <c r="R51" t="n">
-        <v>7274781</v>
+        <v>7274861</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6094,22 +5692,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2021-05-05</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>19:00</t>
+          <t>2020-01-15</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2021-05-05</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>19:00</t>
+          <t>2020-01-17</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6124,31 +5712,26 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Max Jonsson</t>
+          <t>Elin Lindmark</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Max Jonsson</t>
+          <t>Isak Sarac</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121533119</v>
+        <v>121477319</v>
       </c>
       <c r="B52" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -6169,18 +5752,14 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Sorsele, Ly lm</t>
+          <t>Jiltjaurberget, Ly lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>586262</v>
+        <v>586263</v>
       </c>
       <c r="R52" t="n">
         <v>7274991</v>
@@ -6210,22 +5789,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2021-05-05</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>20:00</t>
+          <t>2020-01-15</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2021-05-05</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>20:00</t>
+          <t>2020-01-17</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6240,49 +5809,44 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Max Jonsson</t>
+          <t>Elin Lindmark</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Max Jonsson</t>
+          <t>Isak Sarac</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121532444</v>
+        <v>121533106</v>
       </c>
       <c r="B53" t="n">
-        <v>79698</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -6296,10 +5860,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>586241</v>
+        <v>586385</v>
       </c>
       <c r="R53" t="n">
-        <v>7274946</v>
+        <v>7274744</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6331,7 +5895,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6341,7 +5905,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6368,37 +5932,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121532446</v>
+        <v>121533112</v>
       </c>
       <c r="B54" t="n">
-        <v>79698</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -6412,10 +5971,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>586289</v>
+        <v>586773</v>
       </c>
       <c r="R54" t="n">
-        <v>7274978</v>
+        <v>7274818</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6447,7 +6006,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6457,7 +6016,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6484,37 +6043,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121532443</v>
+        <v>121533115</v>
       </c>
       <c r="B55" t="n">
-        <v>79698</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -6528,10 +6082,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>586360</v>
+        <v>586409</v>
       </c>
       <c r="R55" t="n">
-        <v>7274887</v>
+        <v>7274860</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6563,7 +6117,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6573,7 +6127,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6600,19 +6154,14 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121533112</v>
+        <v>121533119</v>
       </c>
       <c r="B56" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -6644,10 +6193,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>586773</v>
+        <v>586262</v>
       </c>
       <c r="R56" t="n">
-        <v>7274818</v>
+        <v>7274991</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6679,7 +6228,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6689,7 +6238,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6716,15 +6265,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121532533</v>
+        <v>95057648</v>
       </c>
       <c r="B57" t="n">
-        <v>79697</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6749,24 +6293,21 @@
           <t>(L.) Hoffm.</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>586423</v>
+        <v>586391</v>
       </c>
       <c r="R57" t="n">
-        <v>7274746</v>
+        <v>7274870</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6790,22 +6331,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2021-05-05</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>20:00</t>
+          <t>2021-07-24</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2021-05-05</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>20:00</t>
+          <t>2021-07-24</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6820,27 +6351,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Max Jonsson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Max Jonsson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121532632</v>
+        <v>95057696</v>
       </c>
       <c r="B58" t="n">
-        <v>90724</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6848,41 +6374,38 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>586372</v>
+        <v>586434</v>
       </c>
       <c r="R58" t="n">
-        <v>7275002</v>
+        <v>7274861</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6906,22 +6429,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2021-05-05</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>23:00</t>
+          <t>2021-07-24</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2021-05-05</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>23:00</t>
+          <t>2021-07-24</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6936,66 +6449,57 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Max Jonsson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Max Jonsson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121532208</v>
+        <v>121476718</v>
       </c>
       <c r="B59" t="n">
-        <v>91290</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Sorsele, Ly lm</t>
+          <t>Jiltjaurberget, Ly lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>586434</v>
+        <v>586671</v>
       </c>
       <c r="R59" t="n">
-        <v>7274786</v>
+        <v>7274637</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7022,22 +6526,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2021-05-05</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2020-01-15</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2021-05-05</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2020-01-17</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7052,15 +6546,961 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Isak Sarac</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>121476719</v>
+      </c>
+      <c r="B60" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Jiltjaurberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>586424</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7274747</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2020-01-15</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2020-01-17</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Isak Sarac</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>121476720</v>
+      </c>
+      <c r="B61" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Jiltjaurberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>586428</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7274782</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2020-01-15</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2020-01-17</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Isak Sarac</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>121476721</v>
+      </c>
+      <c r="B62" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Jiltjaurberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>586434</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7274787</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2020-01-15</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2020-01-17</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Isak Sarac</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>121532532</v>
+      </c>
+      <c r="B63" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Sorsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>586670</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7274637</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
           <t>Max Jonsson</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
+      <c r="AX63" t="inlineStr">
         <is>
           <t>Max Jonsson</t>
         </is>
       </c>
-      <c r="AY59" t="inlineStr"/>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>121532533</v>
+      </c>
+      <c r="B64" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Sorsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>586423</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7274746</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>121532534</v>
+      </c>
+      <c r="B65" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Sorsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>586428</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7274781</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>121532535</v>
+      </c>
+      <c r="B66" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Sorsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>586434</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7274786</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>95057551</v>
+      </c>
+      <c r="B67" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Sorsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>586391</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7274870</v>
+      </c>
+      <c r="S67" t="n">
+        <v>25</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2021-07-24</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2021-07-24</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>95057883</v>
+      </c>
+      <c r="B68" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Sorsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>586545</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7274947</v>
+      </c>
+      <c r="S68" t="n">
+        <v>25</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2021-07-24</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2021-07-24</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
